--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1680,6 +1680,186 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Expedia News</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Expedia+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/the-expedia-taap-a-behind-the-scenes-engine-for-us-travel-advisors/69667174</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:43:26</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Expedia, Expedia TAAP</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Expedia (Brand) | Expedia TAAP (Brand)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>The Expedia TAAP. A behind-the-scenes engine for US travel advisors - AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZWljUkE5bENzblZXYkV3M243TW93dHpJeUhSS18wT0pzZTZQMWZRek9qaUN6RVdQcko4TTZyaTJCWlZ3Y0tRTl83UUpNSmoyckdEc28zOV80c2V1akoxWnhKaFJFa19jbzExZFlSWnBJUWtVQXZlNnVBNDFrR3JQbDN3TFpkQklWZVNLQTFJdFNwWm9rNERHbmktbGIyTnZDNHJoZ0F5bTJJOENsZ0FhOEFsUHZWNnRhR1pzZjhYZ0hNaWs?oc=5" target="_blank"&gt;The Expedia TAAP. A behind-the-scenes engine for US travel advisors&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;AD HOC NEWS&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:41:58</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Expedia, Expedia TAAP executed general travel news movement impacting Abhee, Mondee market segment</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Standard market activity by Expedia, Expedia TAAP. No direct action required for Abhee, Mondee.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>The Expedia TAAP. A behind-the-scenes engine for US travel advisors&amp;nbsp;&amp;nbsp;AD HOC NEWS.</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Abhee, Mondee</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Google News Search - Expedia (Expedia)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Expedia%22%20after%3A2026-06-30&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZWljUkE5bENzblZXYkV3M243TW93dHpJeUhSS18wT0pzZTZQMWZRek9qaUN6RVdQcko4TTZyaTJCWlZ3Y0tRTl83UUpNSmoyckdEc28zOV80c2V1akoxWnhKaFJFa19jbzExZFlSWnBJUWtVQXZlNnVBNDFrR3JQbDN3TFpkQklWZVNLQTFJdFNwWm9rNERHbmktbGIyTnZDNHJoZ0F5bTJJOENsZ0FhOEFsUHZWNnRhR1pzZjhYZ0hNaWs?oc=5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:43:26</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Expedia, Expedia TAAP</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Expedia (Brand) | Expedia TAAP (Brand)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>The Expedia TAAP. A behind-the-scenes engine for US travel advisors - AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZWljUkE5bENzblZXYkV3M243TW93dHpJeUhSS18wT0pzZTZQMWZRek9qaUN6RVdQcko4TTZyaTJCWlZ3Y0tRTl83UUpNSmoyckdEc28zOV80c2V1akoxWnhKaFJFa19jbzExZFlSWnBJUWtVQXZlNnVBNDFrR3JQbDN3TFpkQklWZVNLQTFJdFNwWm9rNERHbmktbGIyTnZDNHJoZ0F5bTJJOENsZ0FhOEFsUHZWNnRhR1pzZjhYZ0hNaWs?oc=5" target="_blank"&gt;The Expedia TAAP. A behind-the-scenes engine for US travel advisors&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;AD HOC NEWS&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:42:56</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Expedia, Expedia TAAP executed general travel news movement impacting Abhee, Mondee market segment</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Standard market activity by Expedia, Expedia TAAP. No direct action required for Abhee, Mondee.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>The Expedia TAAP. A behind-the-scenes engine for US travel advisors&amp;nbsp;&amp;nbsp;AD HOC NEWS.</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Abhee, Mondee</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1860,6 +1860,229 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Booking.com News</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Booking.com%22+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/the-priceline-partner-network-booking-holdings-pushes-white-label-travel/69671933</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-07-02 10:32:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Priceline Partner Network</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Priceline Partner Network (Brand)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>The Priceline Partner Network - Booking Holdings pushes white-label travel for US brands - AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Redaktion ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>By Julian Reed, ad hoc news Software &amp; Services Desk. Reviewed July 02, 2026, 6:31 AM ET. Details in the imprint.
+Priceline Partner Network from Booking Holdings is the sort of product you notice only when it fails: the flight and hotel widgets tucked into your bank app or newspaper website suddenly feel slower, prices jump, and you wonder who is really running the engine behind the scenes. On a recent test in a US airline loyalty portal, the white-labeled interface looked nothing like Priceline, yet the search results, filters and bundled deals behaved exactly like a modern online travel agency.
+Priceline Partner Network is Booking Holdings' white-label and affiliate platform that lets other brands embed Priceline's hotel, flight and car rental inventory into their own websites and apps, usually under the partner's logo and color scheme rather than Priceline's. US banks, media companies and loyalty programs use it to offer travel booking without building a full agency from scratch. According to Priceline, partners can integrate via APIs, customizable widgets or full white-label sites that run on Priceline's back-end while carrying the partner's branding.
+On the official Partner Network overview, Priceline pitches the service in straightforward terms: access to more than a million accommodations worldwide, competitive commission structures and around-the-clock support teams for partner integrations. A recent case-study style blog post from Booking Holdings highlights how one North American financial institution plugged Priceline Partner Network into its rewards portal to let cardholders redeem points for hotels and flights, describing measurable increases in travel redemptions and portal engagement. In that example, the institution's product lead notes that "our customers see our name and our rewards currency, but they are effectively booking on Priceline under the hood," underscoring the invisible, infrastructure-like role of the product.
+For a broader view of Booking Holdings' online travel ecosystem and how products like Priceline Partner Network fit into the group's long-term strategy, visit the dedicated topic section and investor relations site.
+For US brands thinking about bolting travel booking onto an existing app, the main entry point is the Priceline Partner Network developer and partner documentation. There, Booking Holdings outlines several technical options: REST-style APIs for hotel, flight and car search; turnkey white-label sites hosted by Priceline; and embeddable widgets that can be dropped into a web page with minimal code. In practice, that means a credit card rewards portal or a regional news outlet can add a "Book travel" tab that talks directly to Priceline's systems.
+From a user's perspective, the experience often starts with a familiar loyalty or banking login, followed by a travel search interface that feels polished and relatively fast. On a test through a US card issuer's travel portal known to be powered by Priceline, hotel results in New York loaded in under three seconds on a standard home broadband connection, with filter options for star rating, neighborhood and free cancellation. The booking confirmation email carried the issuer's logo but embedded a "powered by Priceline" notice in small type at the bottom, a subtle reminder of whose technology sits behind the scenes.
+Booking Holdings does not list public commission tables for Priceline Partner Network, but industry affiliate marketing portals and partner recruitment pages suggest that partners typically earn a percentage of Priceline's margin on completed bookings, with hotel commission rates varying by property and channel. For large enterprise partners, Booking Holdings appears to negotiate custom structures based on booking volume and integration depth, according to commentary from travel-tech consultants who have implemented similar white-label solutions. In many cases, the partner takes on the customer relationship while Priceline manages supply contracts, payment processing and customer service escalation.
+That division of labor matters for risk and cost. A US media site that embeds a travel search tool does not need to sign individual contracts with thousands of hotels or airlines, nor handle PCI-compliant payment infrastructure; Priceline provides those capabilities. At the same time, if a hotel stay goes badly or a flight is disrupted, the end user may blame the media site or bank, even though the booking mechanics were powered by Priceline. Booking Holdings' CEO Glenn Fogel has spoken in earnings calls about the group's efforts to improve post-booking service quality and communication across its brands, implicitly covering partner-driven channels as well.
+Priceline Partner Network competes in a crowded space of white-label travel tools. Expedia Group runs Expedia Partner Solutions, formerly known as Expedia Affiliate Network, which offers similar API and white-label site options for hotels and flights. Smaller specialists such as Duffel and Travix focus on flight content and NDC integrations, serving fintechs and loyalty programs that want more control over airline-specific offers. In this field, Booking Holdings leverages its massive accommodation inventory from Booking.com and Priceline to pitch depth of choice and flexible cancellation policies as differentiators for partners.
+Analyst notes from travel-sector research firms often describe white-label and affiliate businesses as "high-margin, low-brand" segments: Booking Holdings earns revenue from bookings it does not have to market directly, while partners take care of customer acquisition. In recent filings, Booking Holdings lists advertising and other revenue, which includes affiliate and partner programs, as a meaningful contributor alongside core merchant and agency revenues. While the company does not break out Priceline Partner Network separately, management commentary points to ongoing investment in partner-facing tools and APIs, a sign that the segment is strategically relevant.
+For US travelers, the question is less "should I use Priceline Partner Network" and more "am I comfortable booking through my bank or a media site using a third-party engine." Privacy policies on several US partner sites that use Priceline mention data sharing with travel service providers, including anonymized search data and personal details required for booking. In many cases, Booking Holdings acts as the merchant of record or travel agent, meaning it receives traveler names, dates, and payment information, subject to its own privacy policy. Partners typically disclose this in their terms and conditions or in small-print disclaimers on booking pages.
+In practice, the data flows mirror a regular booking on Priceline or Booking.com, but with an extra interface layer. On a booking test through a US cashback portal tied to Priceline, the payment page explicitly stated that the transaction would be processed by Priceline as the travel agent, even though the portal's branding dominated the screen. That alignment allows Booking Holdings to use its own risk, fraud and customer service infrastructure, which Fogel has said is crucial to maintaining profitability in a volatile travel environment.
+For Booking Holdings, Priceline Partner Network is one of several quieter engines that help the group monetize its scale in travel inventory while diversifying beyond direct-to-consumer channels. The product taps partners from finance, media and loyalty programs who may not want to build full travel agencies, yet still wish to offer booking capabilities under their own brands. In aggregate, that can smooth demand across seasons and geographies, supporting revenue resilience beyond peak holiday periods. Shares of Booking Holdings (NASDAQ: BKNG) give investors exposure to this partner-based segment alongside higher-profile consumer brands like Booking.com and Priceline.
+This article was AI-assisted and editorially reviewed. Product information is provided without warranty; prices and availability may change at short notice. Not investment advice and not a buy or sell recommendation. Securities trading carries risks up to total loss.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:44</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Priceline Partner Network executed m&amp;a movement impacting Mondee market segment</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Potential opportunity. Competitor Priceline Partner Network is undergoing stress (m&amp;a) which Mondee can capitalize on.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>By Julian Reed, ad hoc news Software &amp; Services Desk. Reviewed July 02, 2026, 6:31 AM ET.</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Booking.com News</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Booking.com%22+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/the-priceline-partner-network-from-booking-holdings-inc-white-label/69669237</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-07-01 17:00:02</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Priceline Partner Network</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Priceline Partner Network (Brand)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>The Priceline Partner Network from Booking Holdings Inc. - White-label travel engine quietly powers - AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Redaktion ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>By Nora Whitfield, ad hoc news Accessories &amp; Components Desk. Reviewed July 01, 2026, 12:59 PM ET. Details in the imprint.
+Priceline Partner Network from Booking Holdings Inc. is the kind of travel tech product you only notice when it fails. I watched a demo on a partner’s staging site: hotel cards snap into place, blue buttons pulse, and a Los Angeles weekend quote recalculates in under a second.
+Priceline Partner Network is a white-label travel booking platform that lets other brands embed Priceline’s hotel, flight, car, and package inventory into their own sites and apps. Priceline supplies the search engine, inventory, and pricing; the partner controls branding and customer relationship.
+Booking Holdings describes the offering as an affiliate and API-based solution that taps into Priceline’s negotiated deals, including Express Deals and discounted rates that are typically visible on Priceline.com itself. The same backend can power custom banners, recommendation widgets, or full white-label booking journeys inside a partner’s environment.
+In the US, Priceline Partner Network is pitched heavily to publishers, loyalty programs, and financial institutions that want travel booking as a feature but don’t want to build it from scratch. Affiliates can start with a simple referral model, while larger partners integrate via APIs or hosted white-label flows.
+Recent partnerships have included media sites, airline and hotel loyalty programs, and travel content platforms, though many run under the partner’s brand and never mention Priceline directly. During the demo, a product manager at a US media group showed how they dropped in a hotel search widget above an article; the widget quietly called Priceline’s API under the hood.
+More on how Booking Holdings Inc. uses platforms like Priceline Partner Network to extend its reach beyond its own consumer sites.
+Underneath the clean front-end, Priceline Partner Network is essentially an integration layer on top of Priceline’s own booking stack. Partners can choose hosted pages that look like their brand but are operated by Priceline, or deeper API integrations that keep traffic fully on the partner domain.
+The core components are standardized: search forms, result lists, filters, maps, and checkout screens. In the demo, I typed "New York" into a white-label search bar; autocomplete flickered through Manhattan and borough names, while the results page loaded a grid of hotels with thumbnail photos, star ratings, and final prices in US dollars.
+Booking Holdings reports more than 28 million listings across its brands, including Booking.com, Priceline, and Agoda. Priceline Partner Network taps a subset of that inventory that is relevant for US travelers, primarily hotels and other lodging plus certain flight and car rental options.
+Partners can configure which inventory types they want to surface. A credit card rewards program might focus on hotels and car rentals, while a travel editor’s site might emphasize short city stays and last-minute deals. In all cases, the pricing logic remains with Priceline, including promotional rates and opaque Express Deals.
+Economically, Priceline Partner Network runs on revenue share and commission models. The partner earns a cut of completed bookings, while Priceline retains margin for sourcing and servicing the travel product. Exact percentages are negotiated and depend on scale, integration depth, and vertical.
+In affiliate-style implementations, partners mainly drive traffic to Priceline-hosted pages and are paid on performance. In deeper white-label models, Priceline provides more tailored technical support and may collaborate on marketing campaigns, but the commission framework remains core.
+From a technical perspective, Priceline Partner Network exposes REST-style APIs for search, booking, and content retrieval. Partners authenticate via keys, then call endpoints to retrieve hotel lists, pricing, and availability in near real time. Response payloads include images, metadata, and localized currency displays.
+A senior engineer at Priceline, introduced simply as Mike during a webinar, walked through basic integration steps: register as a partner, receive credentials, hit sandbox APIs, and then move to production once error rates and logging are stable. The sandbox environment mirrors production behavior but uses test cards and dummy bookings.
+Crucially for US brands, Priceline Partner Network lets partners control the look and feel. Logos, colors, typography, and copy are all configurable in hosted flows, and entirely owned by the partner in API-only implementations. Priceline handles the heavy lifting around inventory, payments routing, and fulfillment.
+During the demo, the hotel result cards matched the partner’s brand palette, not Priceline’s familiar blue. A UX specialist from the partner’s team mentioned they had A/B-tested button colors and sort order, while Priceline’s team supplied guidance on best practices based on years of consumer-site optimization.
+Payment processing for bookings made through Priceline Partner Network typically runs through Priceline’s own systems, using major US card networks and alternative payment options where supported. This shields partners from complex PCI compliance and chargeback handling, while still allowing them to track conversions.
+Customer support for the underlying travel product is also handled by Priceline’s service operations, with call centers and chat support that already serve Priceline.com customers. Partners can integrate co-branded help pages or simply hand off users to Priceline’s support channels after booking.
+Data sharing is a significant part of the value proposition. Partners receive aggregated performance metrics: searches, clicks, bookings, revenue, and commission totals. Advanced integrations can also pass back attribution tags that tie booking behavior to specific content pages or marketing campaigns.
+In a case study shared in a webinar, a US digital publisher reportedly saw double-digit growth in time on page after adding a hotel widget below their city guides. The publisher’s analytics showed that users who interacted with the widget were more likely to return to the site, reinforcing both ad and affiliate revenue.
+Brand-conscious partners need to factor in the trade-offs. On one hand, they gain a mature booking engine and deep inventory without capital expenditure on travel tech. On the other, they rely on Priceline’s service quality and must ensure that white-label flows align with their own privacy policies and user expectations.
+Ben Harrell, Chief Marketing Officer of Booking Holdings’ North American operations for the Booking.com brand, has often emphasized in interviews that trust is central to the group’s value proposition. That trust needs to extend to white-label experiences, where users may not even realize Priceline is behind the scenes.
+The white-label travel space is not empty. Other major groups and specialist aggregators offer similar affiliate and API programs for hotels and flights. For US brands, the choice often comes down to inventory breadth, commission rates, technical support, and the reliability of the underlying booking infrastructure.
+Booking Holdings’ scale gives Priceline Partner Network a competitive angle: the same supply relationships that power Booking.com, Priceline, and Agoda can feed partner sites. That means partners piggyback on negotiated rates and availability that a smaller player might struggle to match.
+For US retail investors, Priceline Partner Network matters less as a consumer brand and more as a distribution channel. It pushes Booking Holdings beyond its own sites into other companies’ ecosystems, broadening the funnel for travel bookings. That can diversify demand and reduce reliance on direct or paid-search traffic.
+Glenn Fogel, CEO of Booking Holdings, has repeatedly highlighted platform and partnership strategies in earnings calls as part of the group’s long-term growth story. These initiatives include affiliate programs, B2B distribution, and payments services alongside core consumer brands.
+Booking Holdings Inc. operates a portfolio of online travel brands, including Booking.com, Priceline, Agoda, Rentalcars.com, and KAYAK, with a strong focus on lodging. Priceline Partner Network fits into the group’s B2B and affiliate segment, extending reach while leveraging existing technology and supply.
+Booking Holdings Inc. stock (NASDAQ: BKNG, ISIN US09857L1089) is closely watched as a proxy for global online travel demand, with B2B platforms like Priceline Partner Network forming part of the broader revenue and margin mix reported to investors.
+This article was AI-assisted and editorially reviewed. Product information is provided without warranty; prices and availability may change at short notice. Not investment advice and not a buy or sell recommendation. Securities trading carries risks up to total loss.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:44</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Priceline Partner Network executed funding movement impacting Mondee market segment</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Standard market activity by Priceline Partner Network. No direct action required for Mondee.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>By Nora Whitfield, ad hoc news Accessories &amp; Components Desk. Reviewed July 01, 2026, 12:59 PM ET.</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
           <t>Target_Brand</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Criticality_Score</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Priority_Tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -609,6 +619,14 @@
           <t>Abhee, Mondee</t>
         </is>
       </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -697,6 +715,14 @@
       <c r="R3" t="inlineStr">
         <is>
           <t>Mondee</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
         </is>
       </c>
     </row>
@@ -796,6 +822,14 @@
           <t>Abhee, Mondee</t>
         </is>
       </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -886,6 +920,14 @@
           <t>Abhee, Mondee</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -977,6 +1019,14 @@
       <c r="R6" t="inlineStr">
         <is>
           <t>Abhee, Mondee</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
         </is>
       </c>
     </row>
@@ -1074,6 +1124,14 @@
           <t>Abhee, Mondee</t>
         </is>
       </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1167,6 +1225,14 @@
       <c r="R8" t="inlineStr">
         <is>
           <t>Abhee, Mondee</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
         </is>
       </c>
     </row>
@@ -1263,6 +1329,14 @@
       <c r="R9" t="inlineStr">
         <is>
           <t>Abhee, Mondee</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
         </is>
       </c>
     </row>
@@ -1386,6 +1460,14 @@
           <t>Abhee, Mondee</t>
         </is>
       </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1492,6 +1574,14 @@
           <t>Abhee, Mondee</t>
         </is>
       </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1589,6 +1679,14 @@
           <t>Abhee, Mondee</t>
         </is>
       </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1679,6 +1777,14 @@
           <t>Abhee, Mondee</t>
         </is>
       </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1769,6 +1875,14 @@
           <t>Abhee, Mondee</t>
         </is>
       </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1857,6 +1971,14 @@
       <c r="R15" t="inlineStr">
         <is>
           <t>Abhee, Mondee</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
         </is>
       </c>
     </row>
@@ -1961,6 +2083,14 @@
       <c r="R16" t="inlineStr">
         <is>
           <t>Mondee</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>13</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
         </is>
       </c>
     </row>
@@ -2082,6 +2212,14 @@
           <t>Mondee</t>
         </is>
       </c>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2221,6 +2221,202 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Downtown Travel News</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Downtown+Travel%22+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.travelandtourworld.com/news/article/eicjy8292lw4/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:03:54</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Downtown Travel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Downtown Travel (Brand)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Explore Vancouver’s Car-Free Granville Street This Summer as Pedestrian Zone Expansion Creates a New Downtown Travel Experience - Travel And Tour World</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMibkFVX3lxTE9KR2NQal9rTGpOaUdtR0prbk1nWWwybmZ1VGRlNjZ2Y1o1ZVRlYkN2RU9Vd25odVFWVlBMbDhmc3k4bk10STN2bm43WjdyaWhnMlMwZHZSWkF5bnE0cEJvTDFqRGZnRFMzX2FzMjhn?oc=5" target="_blank"&gt;Explore Vancouver’s Car-Free Granville Street This Summer as Pedestrian Zone Expansion Creates a New Downtown Travel Experience&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Travel And Tour World&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:56:12</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Downtown Travel executed general travel news movement impacting Mondee market segment</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Standard market activity by Downtown Travel. No direct action required for Mondee.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Explore Vancouver’s Car-Free Granville Street This Summer as Pedestrian Zone Expansion Creates a New Downtown Travel Experience&amp;nbsp;&amp;nbsp;Travel And Tour World.</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Google News Search - Downtown Travel (Downtown Travel)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Downtown%20Travel%22%20after%3A2026-07-02&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9KR2NQal9rTGpOaUdtR0prbk1nWWwybmZ1VGRlNjZ2Y1o1ZVRlYkN2RU9Vd25odVFWVlBMbDhmc3k4bk10STN2bm43WjdyaWhnMlMwZHZSWkF5bnE0cEJvTDFqRGZnRFMzX2FzMjhn?oc=5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:03:54</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Downtown Travel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Downtown Travel (Brand)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Explore Vancouver’s Car-Free Granville Street This Summer as Pedestrian Zone Expansion Creates a New Downtown Travel Experience - Travel And Tour World</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMibkFVX3lxTE9KR2NQal9rTGpOaUdtR0prbk1nWWwybmZ1VGRlNjZ2Y1o1ZVRlYkN2RU9Vd25odVFWVlBMbDhmc3k4bk10STN2bm43WjdyaWhnMlMwZHZSWkF5bnE0cEJvTDFqRGZnRFMzX2FzMjhn?oc=5" target="_blank"&gt;Explore Vancouver’s Car-Free Granville Street This Summer as Pedestrian Zone Expansion Creates a New Downtown Travel Experience&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Travel And Tour World&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:56:38</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Downtown Travel executed general travel news movement impacting Mondee market segment</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Standard market activity by Downtown Travel. No direct action required for Mondee.</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Explore Vancouver’s Car-Free Granville Street This Summer as Pedestrian Zone Expansion Creates a New Downtown Travel Experience&amp;nbsp;&amp;nbsp;Travel And Tour World.</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2417,6 +2417,104 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Expedia News</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Expedia+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.travelpress.com/expedia-taap-adds-new-back-office-api-and-tools/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-07-06 13:21:25</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Expedia, Expedia TAAP</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Expedia (Brand) | Expedia TAAP (Brand)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Expedia TAAP adds new back-office API and tools - TravelPress</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMiggFBVV95cUxPeWdaYlhrSlNXcEdTbjl5RW5QY0xwUS1nYjNodW92aEd0U1cyQlNMd3p0VGlTZXkyRzg1OVY2UFhrS3BMS2hQZVI4Ql9iNURyR2EzNTlXV01kcmwtcWt4NU1WYkxYZHFRYjVnSWlwWlZRZzBPaF9vb2VEanAzd3c0NkVR?oc=5" target="_blank"&gt;Expedia TAAP adds new back-office API and tools&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TravelPress&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-06 18:00:03</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Expedia, Expedia TAAP executed general travel news movement impacting Abhee, Mondee market segment</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Standard market activity by Expedia, Expedia TAAP. No direct action required for Abhee, Mondee.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Expedia TAAP adds new back-office API and tools&amp;nbsp;&amp;nbsp;TravelPress.</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Abhee, Mondee</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_News" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Raw_News'!$A$1:$T$20</definedName>
+  </definedNames>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,7 +27,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,10 +50,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -62,7 +75,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -426,7 +439,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -486,7 +499,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>News_Category</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -586,7 +599,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>General Travel News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -601,7 +614,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed general travel news movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed product announcement movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -684,7 +697,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>General Travel News</t>
+          <t>General Industry News</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -699,7 +712,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Downtown Travel executed general travel news movement impacting Mondee market segment</t>
+          <t>Downtown Travel executed general industry news movement impacting Mondee market segment</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -772,8 +785,8 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Posted
-by Ronan Daniel
+          <t>Posted_x000D_
+by Ronan Daniel_x000D_
 on                                Jun 19th, 2026 at 14:17
 New API and custom booking IDs for agencies
 Expedia Group’s Travel Agent Affiliate Program (TAAP), the group’s B2B programme for agencies, has equipped its platform with new tools: a back-office API and a feature that lets agencies add their own internal reference number to bookings. The programme frames the move as a shift from a simple booking tool to a more connected ecosystem. The aim is to cut manual work, improve booking tracking and revenue reconciliation, and give travel advisors tools that plug into their existing software.
@@ -789,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Product Launch</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -804,12 +817,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed product launch movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed product announcement movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>High competitive activity. Monitor Expedia, Expedia TAAP's product launch closely and evaluate defense strategies for Abhee, Mondee.</t>
+          <t>High competitive activity. Monitor Expedia, Expedia TAAP's product announcement closely and evaluate defense strategies for Abhee, Mondee.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -887,7 +900,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Product Launch</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -902,7 +915,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed product launch movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed product announcement movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -988,7 +1001,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>General Travel News</t>
+          <t>General Industry News</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1003,7 +1016,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed general travel news movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed general industry news movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1091,7 +1104,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Product Launch</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1106,7 +1119,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed product launch movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed product announcement movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1194,7 +1207,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Funding</t>
+          <t>Leadership Changes</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1204,17 +1217,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed funding movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed leadership changes movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Moderate competitive movement. Assess Abhee, Mondee's product positioning relative to Expedia, Expedia TAAP.</t>
+          <t>Standard market activity by Expedia, Expedia TAAP. No direct action required for Abhee, Mondee.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1298,7 +1311,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Product Launch</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1313,12 +1326,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed product launch movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed product announcement movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>High competitive activity. Monitor Expedia, Expedia TAAP's product launch closely and evaluate defense strategies for Abhee, Mondee.</t>
+          <t>High competitive activity. Monitor Expedia, Expedia TAAP's product announcement closely and evaluate defense strategies for Abhee, Mondee.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1427,7 +1440,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Funding</t>
+          <t>General Industry News</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1437,17 +1450,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed funding movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed general industry news movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Moderate competitive movement. Assess Abhee, Mondee's product positioning relative to Expedia, Expedia TAAP.</t>
+          <t>Standard market activity by Expedia, Expedia TAAP. No direct action required for Abhee, Mondee.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1541,7 +1554,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Product Launch</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1556,12 +1569,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed product launch movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed product announcement movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>High competitive activity. Monitor Expedia, Expedia TAAP's product launch closely and evaluate defense strategies for Abhee, Mondee.</t>
+          <t>High competitive activity. Monitor Expedia, Expedia TAAP's product announcement closely and evaluate defense strategies for Abhee, Mondee.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1646,7 +1659,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Product Launch</t>
+          <t>Leadership Changes</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1656,17 +1669,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed product launch movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed leadership changes movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>High competitive activity. Monitor Expedia, Expedia TAAP's product launch closely and evaluate defense strategies for Abhee, Mondee.</t>
+          <t>Standard market activity by Expedia, Expedia TAAP. No direct action required for Abhee, Mondee.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1744,7 +1757,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Product Launch</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1759,7 +1772,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed product launch movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed product announcement movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,7 +1855,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>General Travel News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1857,7 +1870,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed general travel news movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed product announcement movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1940,7 +1953,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>General Travel News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1955,7 +1968,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed general travel news movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed product announcement movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2052,7 +2065,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>General Industry News</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2067,12 +2080,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Priceline Partner Network executed m&amp;a movement impacting Mondee market segment</t>
+          <t>Priceline Partner Network executed general industry news movement impacting Mondee market segment</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Potential opportunity. Competitor Priceline Partner Network is undergoing stress (m&amp;a) which Mondee can capitalize on.</t>
+          <t>Potential opportunity. Competitor Priceline Partner Network is undergoing stress (general industry news) which Mondee can capitalize on.</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2179,7 +2192,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Funding</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2194,7 +2207,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Priceline Partner Network executed funding movement impacting Mondee market segment</t>
+          <t>Priceline Partner Network executed product announcement movement impacting Mondee market segment</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2277,7 +2290,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>General Travel News</t>
+          <t>Strategic Expansion or Changes</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2287,17 +2300,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Downtown Travel executed general travel news movement impacting Mondee market segment</t>
+          <t>Downtown Travel executed strategic expansion or changes movement impacting Mondee market segment</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Standard market activity by Downtown Travel. No direct action required for Mondee.</t>
+          <t>Moderate competitive movement. Assess Mondee's product positioning relative to Downtown Travel.</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2375,7 +2388,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>General Travel News</t>
+          <t>General Industry News</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2390,7 +2403,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Downtown Travel executed general travel news movement impacting Mondee market segment</t>
+          <t>Downtown Travel executed general industry news movement impacting Mondee market segment</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2473,7 +2486,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>General Travel News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2488,7 +2501,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Expedia, Expedia TAAP executed general travel news movement impacting Abhee, Mondee market segment</t>
+          <t>Expedia, Expedia TAAP executed product announcement movement impacting Abhee, Mondee market segment</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2516,6 +2529,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -542,6 +542,11 @@
           <t>Priority_Tier</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>UI_Tab_Mapping</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -604,7 +609,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -633,11 +638,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -702,7 +712,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -731,11 +741,16 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Overview</t>
         </is>
       </c>
     </row>
@@ -836,11 +851,16 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -905,7 +925,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -934,11 +954,16 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1035,11 +1060,16 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Overview</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1139,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1138,11 +1168,16 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1241,11 +1276,16 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Growth</t>
         </is>
       </c>
     </row>
@@ -1345,11 +1385,16 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1481,6 +1526,11 @@
           <t>Tier 4 - Low</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1588,11 +1638,16 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1693,11 +1748,16 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Growth</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1822,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1791,11 +1851,16 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1925,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1889,11 +1954,16 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1958,7 +2028,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1987,11 +2057,16 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2145,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2099,11 +2174,16 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Overview</t>
         </is>
       </c>
     </row>
@@ -2226,11 +2306,16 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -2324,11 +2409,16 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Overview</t>
         </is>
       </c>
     </row>
@@ -2422,11 +2512,16 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Overview</t>
         </is>
       </c>
     </row>
@@ -2520,11 +2615,16 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_News" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CEO_Insights" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Raw_News'!$A$1:$T$20</definedName>
@@ -2632,4 +2633,369 @@
   <autoFilter ref="A1:T20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Filter_Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tab_ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Insight_1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Insight_2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Insight_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TODAY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Market conditions are currently stable.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>No high-priority competitor moves detected in this timeframe.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Continue tracking standard sector intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TODAY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>growth-marketing</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No competitor partnerships or alliances reported.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Venture funding and capital movements are currently quiet.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Monitor standard press channels for upcoming deals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TODAY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>product-strategy</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>No competitor product launches or API releases cataloged.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Digital feature velocity remains normal.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Continue monitoring competitor release notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7D</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Launch a travel‑advisor‑centric API that replicates Expedia TAAP’s behind‑the‑scenes engine, allowing US travel agencies to book and manage itineraries directly through MONDEE’s platform.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Develop a white‑label travel engine for US brands, positioning MONDEE as a direct competitor to Priceline Partner Network’s white‑label offering, and begin outreach to travel agencies seeking a customizable booking solution.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Partner with Vancouver’s tourism board to create and market curated travel packages for the new Car‑Free Granville Street pedestrian zone, using MONDEE’s analytics to target travelers interested in urban experiences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7D</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>growth-marketing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>No competitor partnerships or alliances reported.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Venture funding and capital movements are currently quiet.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Monitor standard press channels for upcoming deals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7D</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>product-strategy</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Develop and launch a proprietary behind‑the‑scenes travel advisor engine that integrates with our existing platform, offering real‑time inventory, dynamic pricing, and a dedicated API for US travel advisors. Include a sandbox environment and partner onboarding program to accelerate adoption.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Introduce a white‑label travel engine solution similar to Priceline Partner Network, enabling travel agencies to brand our booking engine while accessing our inventory and revenue‑management tools. Offer a revenue‑share model and co‑marketing support to attract agencies.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Leverage the new back‑office API and tools announced by Expedia to build a data‑driven analytics dashboard for advisors, highlighting market trends and inventory gaps, positioning MONDEE as the data partner of choice. Pilot the dashboard with a select group of advisors to gather feedback and iterate quickly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Develop a back‑office API suite for travel advisors that offers real‑time inventory and dynamic pricing, directly addressing Expedia TAAP’s new tools and positioning MONDEE as the preferred platform for agency efficiency.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Launch a Vancouver‑centric travel package that highlights the new car‑free Granville Street zone, partnering with local tourism boards to capture the growing demand for sustainable urban travel experiences.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Create a white‑label travel engine tailored for boutique agencies, leveraging insights from Priceline Partner Network’s model to provide a flexible, cost‑effective alternative to Booking Holdings’ offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>growth-marketing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No competitor partnerships or alliances reported.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Venture funding and capital movements are currently quiet.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Monitor standard press channels for upcoming deals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30D</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>product-strategy</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Develop and release a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, to enable agencies to manage bookings and operations directly within MONDEE’s platform.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Launch a dedicated advisor‑efficiency module that automates booking reference generation and workflow management, positioning MONDEE as the most agent‑friendly platform in the market.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing partners to embed MONDEE’s inventory and booking capabilities under their own brand, thereby expanding our distribution network.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and pilot it with our top 10 agency partners to secure early adoption and gather feedback for rapid iteration. This will position MONDEE as the preferred tech partner for agencies seeking streamlined booking and reference management.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Collaborate with Vancouver’s city council to develop a digital promotion package for the new car‑free Granville Street zone, integrating real‑time event data into our platform to drive bookings for local attractions. This partnership will enhance our visibility in the urban travel market and create a unique selling point against competitors.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, offering agencies a customizable booking platform that can be branded and integrated into their own websites, and launch a targeted marketing campaign to agencies in the US and Canada. This will allow us to capture agency revenue streams while leveraging our existing technology stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>growth-marketing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No competitor partnerships or alliances reported.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Venture funding and capital movements are currently quiet.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Monitor standard press channels for upcoming deals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>product-strategy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Develop and launch a dedicated back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, and beta‑test it with a select group of high‑volume advisors to gather feedback before a full rollout. This will position MONDEE as the go‑to platform for agency efficiency and enable early adoption by key partners.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand MONDEE’s booking infrastructure, and market it as a turnkey solution for agencies seeking to expand their product offerings.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Launch a rewards program for agencies that use MONDEE’s API, offering tiered incentives for volume and engagement, to compete with Expedia TAAP’s rewards and drive loyalty.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2765,17 +2765,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Launch a travel‑advisor‑centric API that replicates Expedia TAAP’s behind‑the‑scenes engine, allowing US travel agencies to book and manage itineraries directly through MONDEE’s platform.</t>
+          <t>Develop a proprietary behind‑the‑scenes engine for US travel advisors that matches or exceeds Expedia TAAP’s capabilities, focusing on real‑time inventory, dynamic pricing, and AI‑driven recommendations. Launch a pilot with 10 key agencies within 90 days.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine for US brands, positioning MONDEE as a direct competitor to Priceline Partner Network’s white‑label offering, and begin outreach to travel agencies seeking a customizable booking solution.</t>
+          <t>Create a modular back‑office API suite that allows travel agencies to integrate booking, payment, and reporting workflows directly into their systems, mirroring Expedia TAAP’s new tools, and release a developer portal with SDKs within 60 days.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism board to create and market curated travel packages for the new Car‑Free Granville Street pedestrian zone, using MONDEE’s analytics to target travelers interested in urban experiences.</t>
+          <t>Leverage the new car‑free Granville Street expansion by partnering with local Vancouver tourism boards to curate a ‘Pedestrian‑First’ travel package, including exclusive access to events and local businesses, and promote it through MONDEE’s platform within 30 days.</t>
         </is>
       </c>
     </row>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Develop and launch a proprietary behind‑the‑scenes travel advisor engine that integrates with our existing platform, offering real‑time inventory, dynamic pricing, and a dedicated API for US travel advisors. Include a sandbox environment and partner onboarding program to accelerate adoption.</t>
+          <t>Launch a dedicated 'Mondee Advisor Suite' that provides travel advisors with a back‑office API and real‑time inventory access, mirroring Expedia TAAP, to capture the advisor market and secure early adopters.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine solution similar to Priceline Partner Network, enabling travel agencies to brand our booking engine while accessing our inventory and revenue‑management tools. Offer a revenue‑share model and co‑marketing support to attract agencies.</t>
+          <t>Develop a white‑label travel engine based on MONDEE’s existing booking platform to compete directly with Priceline Partner Network and expand distribution through partner agencies.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Leverage the new back‑office API and tools announced by Expedia to build a data‑driven analytics dashboard for advisors, highlighting market trends and inventory gaps, positioning MONDEE as the data partner of choice. Pilot the dashboard with a select group of advisors to gather feedback and iterate quickly.</t>
+          <t>Accelerate the integration of AI‑driven itinerary optimization into MONDEE’s platform, positioning it as the most personalized solution for advisors and agencies and differentiating from competitors’ generic back‑office tools.</t>
         </is>
       </c>
     </row>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a back‑office API suite for travel advisors that offers real‑time inventory and dynamic pricing, directly addressing Expedia TAAP’s new tools and positioning MONDEE as the preferred platform for agency efficiency.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that includes real‑time booking reference, inventory management, and commission tracking, mirroring Expedia TAAP’s new tools, and beta‑test it with our top 10 agency partners within 90 days.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Launch a Vancouver‑centric travel package that highlights the new car‑free Granville Street zone, partnering with local tourism boards to capture the growing demand for sustainable urban travel experiences.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling third‑party brands to embed MONDEE’s booking platform under their own branding, and secure at least two strategic brand partnerships by Q4.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine tailored for boutique agencies, leveraging insights from Priceline Partner Network’s model to provide a flexible, cost‑effective alternative to Booking Holdings’ offering.</t>
+          <t>Create a ‘Car‑Free Travel Experience’ module that aggregates and promotes pedestrian‑friendly city zones like Vancouver’s Granville Street, and partner with local tourism boards to offer exclusive itineraries, positioning MONDEE as the go‑to platform for sustainable urban travel.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, to enable agencies to manage bookings and operations directly within MONDEE’s platform.</t>
+          <t>Launch a back‑office API for travel advisors that includes real‑time inventory sync and commission optimization, directly addressing the features Expedia TAAP just released.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Launch a dedicated advisor‑efficiency module that automates booking reference generation and workflow management, positioning MONDEE as the most agent‑friendly platform in the market.</t>
+          <t>Form a strategic partnership with a major travel agency network to pilot MONDEE’s new API, ensuring rapid adoption and gathering feedback to refine the tool.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing partners to embed MONDEE’s inventory and booking capabilities under their own brand, thereby expanding our distribution network.</t>
+          <t>Build a white‑label travel engine that offers advanced analytics and AI‑driven recommendations, positioning MONDEE as a differentiated alternative to Priceline Partner Network.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and pilot it with our top 10 agency partners to secure early adoption and gather feedback for rapid iteration. This will position MONDEE as the preferred tech partner for agencies seeking streamlined booking and reference management.</t>
+          <t>Launch a back‑office API and tools for travel advisors that mirrors Expedia TAAP’s new features, enabling agencies to manage bookings, references, and operations directly from our platform. Prioritize integration with major agency software and offer a pilot program to early adopters.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Collaborate with Vancouver’s city council to develop a digital promotion package for the new car‑free Granville Street zone, integrating real‑time event data into our platform to drive bookings for local attractions. This partnership will enhance our visibility in the urban travel market and create a unique selling point against competitors.</t>
+          <t>Collaborate with Vancouver’s city council to create a curated travel package that highlights the new car‑free Granville Street, positioning MONDEE as the go‑to platform for sustainable urban travel experiences. Bundle the experience with exclusive discounts and real‑time navigation updates to attract eco‑conscious travelers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, offering agencies a customizable booking platform that can be branded and integrated into their own websites, and launch a targeted marketing campaign to agencies in the US and Canada. This will allow us to capture agency revenue streams while leveraging our existing technology stack.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand our booking platform while accessing our inventory and APIs. Launch a targeted outreach campaign to mid‑size agencies, offering a revenue‑share model and dedicated support.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, and beta‑test it with a select group of high‑volume advisors to gather feedback before a full rollout. This will position MONDEE as the go‑to platform for agency efficiency and enable early adoption by key partners.</t>
+          <t>Initiate development of a comprehensive back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, and pilot it with a select group of top‑tier advisors to validate integration ease and operational efficiency.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand MONDEE’s booking infrastructure, and market it as a turnkey solution for agencies seeking to expand their product offerings.</t>
+          <t>Design and launch a tiered rewards program for travel advisors, similar to Expedia TAAP Rewards, offering commission boosts and exclusive training, and promote it through industry webinars to quickly onboard advisors.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Launch a rewards program for agencies that use MONDEE’s API, offering tiered incentives for volume and engagement, to compete with Expedia TAAP’s rewards and drive loyalty.</t>
+          <t>Negotiate a white‑label partnership with Priceline Partner Network to embed our booking engine into their platform, enabling us to offer a ready‑made solution to agencies while expanding our reach into the Booking Holdings ecosystem.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2765,17 +2765,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Develop a proprietary behind‑the‑scenes engine for US travel advisors that matches or exceeds Expedia TAAP’s capabilities, focusing on real‑time inventory, dynamic pricing, and AI‑driven recommendations. Launch a pilot with 10 key agencies within 90 days.</t>
+          <t>Partner with Vancouver tourism authorities to create a curated 'Granville Street Experience' package and launch a dedicated mobile feature that highlights the new pedestrian zone, positioning MONDEE as the go-to platform for this unique downtown travel experience.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Create a modular back‑office API suite that allows travel agencies to integrate booking, payment, and reporting workflows directly into their systems, mirroring Expedia TAAP’s new tools, and release a developer portal with SDKs within 60 days.</t>
+          <t>Develop and release a suite of back‑office API tools that provide real‑time inventory, pricing, and analytics, mirroring Expedia TAAP’s new capabilities, to attract travel agencies seeking integrated tech solutions.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leverage the new car‑free Granville Street expansion by partnering with local Vancouver tourism boards to curate a ‘Pedestrian‑First’ travel package, including exclusive access to events and local businesses, and promote it through MONDEE’s platform within 30 days.</t>
+          <t>Initiate a white‑label partnership program targeting US travel brands, offering MONDEE’s booking engine and data services to replicate Priceline’s model and expand our presence in the U.S. market.</t>
         </is>
       </c>
     </row>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Launch a dedicated 'Mondee Advisor Suite' that provides travel advisors with a back‑office API and real‑time inventory access, mirroring Expedia TAAP, to capture the advisor market and secure early adopters.</t>
+          <t>Develop and launch a back‑office API suite that mirrors Expedia TAAP’s new tools, enabling partners to automate inventory, pricing, and booking workflows directly from MONDEE’s platform.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine based on MONDEE’s existing booking platform to compete directly with Priceline Partner Network and expand distribution through partner agencies.</t>
+          <t>Create a rapid integration module that plugs into Expedia TAAP’s API, allowing existing Expedia partners to migrate to MONDEE’s platform with minimal code changes and zero downtime.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Accelerate the integration of AI‑driven itinerary optimization into MONDEE’s platform, positioning it as the most personalized solution for advisors and agencies and differentiating from competitors’ generic back‑office tools.</t>
+          <t>Run a targeted marketing campaign showcasing MONDEE’s advanced analytics and real‑time reporting for back‑office operations, positioning it as a more flexible and cost‑effective alternative to Expedia TAAP’s new offerings.</t>
         </is>
       </c>
     </row>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that includes real‑time booking reference, inventory management, and commission tracking, mirroring Expedia TAAP’s new tools, and beta‑test it with our top 10 agency partners within 90 days.</t>
+          <t>Develop and release a back‑office API that offers real‑time inventory, dynamic pricing, and automated booking reference generation, directly addressing the feature set introduced by Expedia TAAP, and launch a targeted marketing campaign to travel advisors highlighting MONDEE’s superior integration capabilities.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling third‑party brands to embed MONDEE’s booking platform under their own branding, and secure at least two strategic brand partnerships by Q4.</t>
+          <t>Partner with Vancouver’s tourism authority to create a mobile app that guides visitors through the new car‑free Granville Street zone, offering exclusive deals and real‑time navigation, thereby positioning MONDEE as the go‑to platform for the expanded downtown travel experience.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a ‘Car‑Free Travel Experience’ module that aggregates and promotes pedestrian‑friendly city zones like Vancouver’s Granville Street, and partner with local tourism boards to offer exclusive itineraries, positioning MONDEE as the go‑to platform for sustainable urban travel.</t>
+          <t>Build a white‑label travel engine similar to Priceline Partner Network’s model, but with a focus on niche boutique agencies, and offer a revenue‑share partnership to quickly capture market share in the agency segment.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a back‑office API for travel advisors that includes real‑time inventory sync and commission optimization, directly addressing the features Expedia TAAP just released.</t>
+          <t>Deploy a back‑office API that gives travel advisors programmatic access to inventory, booking, and reporting, mirroring Expedia TAAP’s new tools; launch a beta with key agency partners within 60 days. This will position MONDEE as the go‑to platform for agency automation.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Form a strategic partnership with a major travel agency network to pilot MONDEE’s new API, ensuring rapid adoption and gathering feedback to refine the tool.</t>
+          <t>Introduce a white‑label travel engine offering, allowing agencies to embed MONDEE’s booking capabilities under their own brand, similar to Priceline Partner Network; target 10 agencies in the next quarter.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine that offers advanced analytics and AI‑driven recommendations, positioning MONDEE as a differentiated alternative to Priceline Partner Network.</t>
+          <t>Add advisor‑centric features such as automated booking reference generation, real‑time inventory sync, and a streamlined workflow dashboard, directly addressing the efficiency gains highlighted in Expedia TAAP’s launch; roll out the update in 45 days.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a back‑office API and tools for travel advisors that mirrors Expedia TAAP’s new features, enabling agencies to manage bookings, references, and operations directly from our platform. Prioritize integration with major agency software and offer a pilot program to early adopters.</t>
+          <t>Launch a back‑office API suite that mirrors Expedia TAAP’s new tools, adding real‑time inventory visibility and AI‑driven pricing recommendations, and pilot it with 3 high‑volume travel agencies to capture early adopters.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Collaborate with Vancouver’s city council to create a curated travel package that highlights the new car‑free Granville Street, positioning MONDEE as the go‑to platform for sustainable urban travel experiences. Bundle the experience with exclusive discounts and real‑time navigation updates to attract eco‑conscious travelers.</t>
+          <t>Create a dedicated Vancouver travel package that highlights the new car‑free Granville Street, integrating exclusive access passes and local experiences. Promote it through MONDEE’s platform to attract eco‑conscious travelers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand our booking platform while accessing our inventory and APIs. Launch a targeted outreach campaign to mid‑size agencies, offering a revenue‑share model and dedicated support.</t>
+          <t>Offer a white‑label partnership with Priceline Partner Network’s engine, positioning MONDEE as a data‑rich alternative with lower commission rates. Target 5 mid‑market agencies to pilot the solution.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Initiate development of a comprehensive back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, and pilot it with a select group of top‑tier advisors to validate integration ease and operational efficiency.</t>
+          <t>Develop and release a back‑office API suite for travel agencies, mirroring Expedia TAAP’s tools, to enable seamless booking and operational workflows within MONDEE’s platform.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Design and launch a tiered rewards program for travel advisors, similar to Expedia TAAP Rewards, offering commission boosts and exclusive training, and promote it through industry webinars to quickly onboard advisors.</t>
+          <t>Introduce a tiered rewards program for agencies that use MONDEE’s booking engine, similar to Expedia TAAP Rewards, to increase engagement and loyalty.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label partnership with Priceline Partner Network to embed our booking engine into their platform, enabling us to offer a ready‑made solution to agencies while expanding our reach into the Booking Holdings ecosystem.</t>
+          <t>Create a white‑label travel engine offering for partner agencies, leveraging MONDEE’s technology to compete with Priceline Partner Network’s quiet engine.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2765,17 +2765,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Partner with Vancouver tourism authorities to create a curated 'Granville Street Experience' package and launch a dedicated mobile feature that highlights the new pedestrian zone, positioning MONDEE as the go-to platform for this unique downtown travel experience.</t>
+          <t>Launch a ‘Granville Street Experience’ package on MONDEE, partnering with local Vancouver businesses to offer exclusive deals and promote the new pedestrian zone to eco‑conscious travelers.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Develop and release a suite of back‑office API tools that provide real‑time inventory, pricing, and analytics, mirroring Expedia TAAP’s new capabilities, to attract travel agencies seeking integrated tech solutions.</t>
+          <t>Integrate Expedia TAAP’s new back‑office API into MONDEE’s booking system to automate inventory updates and reduce manual data entry, thereby improving operational efficiency and competitiveness.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Initiate a white‑label partnership program targeting US travel brands, offering MONDEE’s booking engine and data services to replicate Priceline’s model and expand our presence in the U.S. market.</t>
+          <t>Conduct a rapid market scan of other cities adopting car‑free zones, then develop a dedicated Urban Mobility travel segment on MONDEE to capture the growing demand for pedestrian‑friendly travel experiences.</t>
         </is>
       </c>
     </row>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite that mirrors Expedia TAAP’s new tools, enabling partners to automate inventory, pricing, and booking workflows directly from MONDEE’s platform.</t>
+          <t>Launch a dedicated back‑office API suite within 90 days that mirrors Expedia TAAP’s new tools, enabling partners to automate inventory, pricing, and booking management directly from MONDEE’s platform, thereby retaining control over critical operational workflows.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Create a rapid integration module that plugs into Expedia TAAP’s API, allowing existing Expedia partners to migrate to MONDEE’s platform with minimal code changes and zero downtime.</t>
+          <t>Develop a real‑time analytics dashboard that ingests data from Expedia TAAP’s new back‑office API, offering partners granular insights into performance metrics and competitive pricing, positioning MONDEE as the data‑driven choice for travel operators.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Run a targeted marketing campaign showcasing MONDEE’s advanced analytics and real‑time reporting for back‑office operations, positioning it as a more flexible and cost‑effective alternative to Expedia TAAP’s new offerings.</t>
+          <t>Initiate a joint pilot program with a select group of Expedia TAAP partners to integrate MONDEE’s booking engine with the new back‑office API, demonstrating seamless interoperability and capturing early adopters before competitors fully leverage the new tools.</t>
         </is>
       </c>
     </row>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API that offers real‑time inventory, dynamic pricing, and automated booking reference generation, directly addressing the feature set introduced by Expedia TAAP, and launch a targeted marketing campaign to travel advisors highlighting MONDEE’s superior integration capabilities.</t>
+          <t>Develop a back‑office API tailored for travel advisors that includes real‑time data on city‑level events such as Vancouver’s car‑free Granville Street, and launch a pilot with a major agency to demonstrate value.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism authority to create a mobile app that guides visitors through the new car‑free Granville Street zone, offering exclusive deals and real‑time navigation, thereby positioning MONDEE as the go‑to platform for the expanded downtown travel experience.</t>
+          <t>Form a partnership with a city tourism board (e.g., Vancouver) to embed MONDEE’s white‑label travel engine into their official travel portal, positioning us as the go‑to platform for local event‑driven itineraries.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine similar to Priceline Partner Network’s model, but with a focus on niche boutique agencies, and offer a revenue‑share partnership to quickly capture market share in the agency segment.</t>
+          <t>Create a dedicated advisor portal offering advanced booking tools and analytics, and launch a targeted marketing campaign to travel agencies highlighting our competitive edge over Expedia TAAP’s new features.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Deploy a back‑office API that gives travel advisors programmatic access to inventory, booking, and reporting, mirroring Expedia TAAP’s new tools; launch a beta with key agency partners within 60 days. This will position MONDEE as the go‑to platform for agency automation.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with MONDEE’s existing booking engine to enable agencies to manage reservations, inventory, and reporting from a single interface. Prioritize API documentation and developer support to accelerate adoption among partner agencies.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine offering, allowing agencies to embed MONDEE’s booking capabilities under their own brand, similar to Priceline Partner Network; target 10 agencies in the next quarter.</t>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand MONDEE’s booking platform and access a full suite of inventory and pricing tools. Bundle this engine with a revenue‑sharing model to attract high‑volume partners.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Add advisor‑centric features such as automated booking reference generation, real‑time inventory sync, and a streamlined workflow dashboard, directly addressing the efficiency gains highlighted in Expedia TAAP’s launch; roll out the update in 45 days.</t>
+          <t>Develop an advisor‑centric dashboard that aggregates real‑time booking data, commission insights, and automated workflow suggestions, addressing the efficiency gains highlighted in Expedia TAAP’s new features. Pilot the dashboard with key agency partners and iterate based on their feedback to ensure it meets their operational needs.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite that mirrors Expedia TAAP’s new tools, adding real‑time inventory visibility and AI‑driven pricing recommendations, and pilot it with 3 high‑volume travel agencies to capture early adopters.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors that includes booking reference tools, real‑time inventory, and dynamic pricing, and immediately pilot it with the top 10 US travel agencies that currently use Expedia TAAP. Position it as a more flexible alternative to Expedia TAAP’s new tools, highlighting faster integration and lower cost.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Create a dedicated Vancouver travel package that highlights the new car‑free Granville Street, integrating exclusive access passes and local experiences. Promote it through MONDEE’s platform to attract eco‑conscious travelers.</t>
+          <t>Create a curated 'Granville Street Experience' travel package that partners with local Vancouver businesses, offering exclusive discounts and guided tours during the car‑free zone expansion. Promote it through targeted social media campaigns to capture the increased tourist traffic.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Offer a white‑label partnership with Priceline Partner Network’s engine, positioning MONDEE as a data‑rich alternative with lower commission rates. Target 5 mid‑market agencies to pilot the solution.</t>
+          <t>Develop a white‑label travel engine that can be integrated into partner sites. Target mid‑tier travel agencies currently using Priceline Partner Network, offering a more customizable and cost‑effective solution.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel agencies, mirroring Expedia TAAP’s tools, to enable seamless booking and operational workflows within MONDEE’s platform.</t>
+          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s booking reference and workflow tools, integrating it with MONDEE’s existing advisor portal to enable seamless agency operations.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for agencies that use MONDEE’s booking engine, similar to Expedia TAAP Rewards, to increase engagement and loyalty.</t>
+          <t>Introduce a tiered rewards program for travel advisors, offering commission boosts and exclusive benefits, to directly compete with Expedia TAAP’s rewards and incentivize partner loyalty.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine offering for partner agencies, leveraging MONDEE’s technology to compete with Priceline Partner Network’s quiet engine.</t>
+          <t>Secure a partnership with a white‑label travel engine (e.g., Priceline Partner Network) to embed its capabilities into MONDEE’s platform, expanding our product suite and providing agencies with a broader inventory without building from scratch.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2765,17 +2765,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Launch a ‘Granville Street Experience’ package on MONDEE, partnering with local Vancouver businesses to offer exclusive deals and promote the new pedestrian zone to eco‑conscious travelers.</t>
+          <t>Conduct a rapid technical assessment of Expedia TAAP's new back‑office API to identify gaps in MONDEE's own API offerings and develop a roadmap to add comparable or superior features within 90 days.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Integrate Expedia TAAP’s new back‑office API into MONDEE’s booking system to automate inventory updates and reduce manual data entry, thereby improving operational efficiency and competitiveness.</t>
+          <t>Initiate a joint API integration pilot with Expedia to enable seamless data exchange for shared partners, positioning MONDEE as a preferred integration partner and mitigating potential loss of business to Expedia.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Conduct a rapid market scan of other cities adopting car‑free zones, then develop a dedicated Urban Mobility travel segment on MONDEE to capture the growing demand for pedestrian‑friendly travel experiences.</t>
+          <t>Launch a targeted marketing campaign highlighting MONDEE's existing back‑office automation strengths and upcoming enhancements, emphasizing our proven ROI and customer support to counter Expedia's new tool rollout.</t>
         </is>
       </c>
     </row>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite within 90 days that mirrors Expedia TAAP’s new tools, enabling partners to automate inventory, pricing, and booking management directly from MONDEE’s platform, thereby retaining control over critical operational workflows.</t>
+          <t>Accelerate development of a back‑office API that supports real‑time inventory, booking, and commission reconciliation across multiple OTAs, positioning it as a more flexible alternative to Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Develop a real‑time analytics dashboard that ingests data from Expedia TAAP’s new back‑office API, offering partners granular insights into performance metrics and competitive pricing, positioning MONDEE as the data‑driven choice for travel operators.</t>
+          <t>Launch a targeted outreach program to agencies currently using Expedia TAAP, offering a free migration toolkit and discounted onboarding to switch to MONDEE’s unified platform.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Initiate a joint pilot program with a select group of Expedia TAAP partners to integrate MONDEE’s booking engine with the new back‑office API, demonstrating seamless interoperability and capturing early adopters before competitors fully leverage the new tools.</t>
+          <t>Conduct a rapid competitive feature gap analysis of Expedia TAAP’s new API, then prioritize and release a complementary feature set (e.g., advanced analytics and automated pricing) within 90 days to differentiate MONDEE’s offering.</t>
         </is>
       </c>
     </row>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a back‑office API tailored for travel advisors that includes real‑time data on city‑level events such as Vancouver’s car‑free Granville Street, and launch a pilot with a major agency to demonstrate value.</t>
+          <t>Launch a dedicated back‑office API platform for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with MONDEE’s existing booking engine to enable agencies to manage reservations, inventory, and reporting from a single dashboard.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Form a partnership with a city tourism board (e.g., Vancouver) to embed MONDEE’s white‑label travel engine into their official travel portal, positioning us as the go‑to platform for local event‑driven itineraries.</t>
+          <t>Secure a partnership with a major city (e.g., Vancouver) to deploy a white‑label travel engine that powers the new car‑free Granville Street pedestrian zone, positioning MONDEE as the preferred tech partner for city‑wide tourism initiatives.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a dedicated advisor portal offering advanced booking tools and analytics, and launch a targeted marketing campaign to travel agencies highlighting our competitive edge over Expedia TAAP’s new features.</t>
+          <t>Develop a mobile app that curates walking‑tour experiences and local events within car‑free zones, and offer it as a value‑add to travel advisors using MONDEE’s platform, capitalizing on the growing demand for sustainable, pedestrian‑friendly travel.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with MONDEE’s existing booking engine to enable agencies to manage reservations, inventory, and reporting from a single interface. Prioritize API documentation and developer support to accelerate adoption among partner agencies.</t>
+          <t>Launch a back‑office API and integrated tools for travel advisors, mirroring Expedia TAAP’s new offerings, and open a beta program for agencies to pilot the solution within the next 30 days.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand MONDEE’s booking platform and access a full suite of inventory and pricing tools. Bundle this engine with a revenue‑sharing model to attract high‑volume partners.</t>
+          <t>Develop a white‑label travel engine for partner agencies, inspired by Priceline Partner Network’s model, to enable agencies to brand and resell our platform, and begin outreach to top 20 agencies by Q3.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Develop an advisor‑centric dashboard that aggregates real‑time booking data, commission insights, and automated workflow suggestions, addressing the efficiency gains highlighted in Expedia TAAP’s new features. Pilot the dashboard with key agency partners and iterate based on their feedback to ensure it meets their operational needs.</t>
+          <t>Create a real‑time booking reference and analytics dashboard for advisors, providing actionable insights and operational efficiency, and roll it out as a premium feature to differentiate from competitors’ new advisor tools.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors that includes booking reference tools, real‑time inventory, and dynamic pricing, and immediately pilot it with the top 10 US travel agencies that currently use Expedia TAAP. Position it as a more flexible alternative to Expedia TAAP’s new tools, highlighting faster integration and lower cost.</t>
+          <t>Launch a back‑office API for travel advisors that offers real‑time inventory, booking reference, and commission tracking, mirroring Expedia TAAP’s new tools but adding a mobile‑first UI and AI‑driven pricing suggestions to differentiate our offering.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Create a curated 'Granville Street Experience' travel package that partners with local Vancouver businesses, offering exclusive discounts and guided tours during the car‑free zone expansion. Promote it through targeted social media campaigns to capture the increased tourist traffic.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network’s platform, enabling boutique agencies to brand our inventory and booking tools while we capture a share of the growing white‑label market.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine that can be integrated into partner sites. Target mid‑tier travel agencies currently using Priceline Partner Network, offering a more customizable and cost‑effective solution.</t>
+          <t>Partner with Vancouver’s city council to create a curated travel package highlighting the new car‑free Granville Street, positioning MONDEE as the go‑to platform for sustainable, city‑centric travel experiences.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s booking reference and workflow tools, integrating it with MONDEE’s existing advisor portal to enable seamless agency operations.</t>
+          <t>Develop and release a back‑office API suite that lets travel advisors manage bookings, inventory, and reporting directly from MONDEE, mirroring Expedia TAAP’s new tools, and pilot it with our top 10 agency partners within 90 days. Include real‑time analytics dashboards and automated commission calculations to reduce manual effort.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for travel advisors, offering commission boosts and exclusive benefits, to directly compete with Expedia TAAP’s rewards and incentivize partner loyalty.</t>
+          <t>Introduce a tiered rewards program for advisors that offers instant cashback, travel credits, and exclusive partner discounts, launching a beta with 50 advisors by Q3 to counter Expedia TAAP’s rewards push.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Secure a partnership with a white‑label travel engine (e.g., Priceline Partner Network) to embed its capabilities into MONDEE’s platform, expanding our product suite and providing agencies with a broader inventory without building from scratch.</t>
+          <t>Secure a white‑label travel engine partnership or build an in‑house engine to provide agencies with a seamless booking interface, positioning MONDEE as a one‑stop solution and leveraging the momentum behind Priceline Partner Network’s quiet rollout.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2765,17 +2765,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Conduct a rapid technical assessment of Expedia TAAP's new back‑office API to identify gaps in MONDEE's own API offerings and develop a roadmap to add comparable or superior features within 90 days.</t>
+          <t>Conduct a rapid technical audit of Expedia TAAP’s new back‑office API to map its capabilities against MONDEE’s current API, then release a version‑2 API that adds missing features such as real‑time inventory sync and automated commission calculations, ensuring partners can migrate without service disruption.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Initiate a joint API integration pilot with Expedia to enable seamless data exchange for shared partners, positioning MONDEE as a preferred integration partner and mitigating potential loss of business to Expedia.</t>
+          <t>Develop a plug‑in that allows MONDEE partners to import data directly from Expedia TAAP’s new tools, positioning MONDEE as the seamless integration layer and encouraging partners to stay within the MONDEE ecosystem while leveraging Expedia’s expanded back‑office functionality.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Launch a targeted marketing campaign highlighting MONDEE's existing back‑office automation strengths and upcoming enhancements, emphasizing our proven ROI and customer support to counter Expedia's new tool rollout.</t>
+          <t>Leverage the new Expedia TAAP API to launch a partner‑centric analytics dashboard that aggregates performance metrics across both platforms, offering insights that Expedia’s tools lack and creating a new subscription revenue stream for MONDEE.</t>
         </is>
       </c>
     </row>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Accelerate development of a back‑office API that supports real‑time inventory, booking, and commission reconciliation across multiple OTAs, positioning it as a more flexible alternative to Expedia TAAP’s new tools.</t>
+          <t>Develop a dedicated connector that maps MONDEE’s inventory and booking data to Expedia TAAP’s new back‑office API, enabling our merchants to sync rates and availability directly with Expedia’s platform.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Launch a targeted outreach program to agencies currently using Expedia TAAP, offering a free migration toolkit and discounted onboarding to switch to MONDEE’s unified platform.</t>
+          <t>Launch a comparative performance study and publish a whitepaper demonstrating that MONDEE’s back‑office automation delivers faster processing times and lower operational costs than Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Conduct a rapid competitive feature gap analysis of Expedia TAAP’s new API, then prioritize and release a complementary feature set (e.g., advanced analytics and automated pricing) within 90 days to differentiate MONDEE’s offering.</t>
+          <t>Propose a joint beta integration program with Expedia, offering early adopters of TAAP’s API exclusive access to MONDEE’s analytics dashboard and priority support, positioning us as the preferred partner for back‑office solutions.</t>
         </is>
       </c>
     </row>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API platform for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with MONDEE’s existing booking engine to enable agencies to manage reservations, inventory, and reporting from a single dashboard.</t>
+          <t>Initiate a rapid development sprint to build a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and launch a beta with a select group of agencies within 90 days to secure early adopters.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Secure a partnership with a major city (e.g., Vancouver) to deploy a white‑label travel engine that powers the new car‑free Granville Street pedestrian zone, positioning MONDEE as the preferred tech partner for city‑wide tourism initiatives.</t>
+          <t>Secure a partnership with Vancouver’s tourism board to embed MONDEE’s real‑time pedestrian‑zone navigation and AR tour features into the Granville Street expansion, positioning us as the preferred tech partner for city‑wide travel experiences.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Develop a mobile app that curates walking‑tour experiences and local events within car‑free zones, and offer it as a value‑add to travel advisors using MONDEE’s platform, capitalizing on the growing demand for sustainable, pedestrian‑friendly travel.</t>
+          <t>Negotiate a white‑label integration with Priceline Partner Network to offer MONDEE’s booking engine to other agencies, expanding our inventory reach and countering their quiet market penetration.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a back‑office API and integrated tools for travel advisors, mirroring Expedia TAAP’s new offerings, and open a beta program for agencies to pilot the solution within the next 30 days.</t>
+          <t>Develop and launch a back‑office API that provides real‑time inventory, booking reference, and commission management for travel advisors, mirroring Expedia TAAP’s new tools, and release it within 90 days to capture the advisor market. Include a developer portal and sample integrations to accelerate adoption.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine for partner agencies, inspired by Priceline Partner Network’s model, to enable agencies to brand and resell our platform, and begin outreach to top 20 agencies by Q3.</t>
+          <t>Negotiate a white‑label partnership with a major travel agency platform, positioning MONDEE’s booking engine as a plug‑and‑play solution similar to Priceline Partner Network’s model, and roll it out in the next quarter. Offer joint marketing and revenue‑sharing terms to incentivize early adoption.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Create a real‑time booking reference and analytics dashboard for advisors, providing actionable insights and operational efficiency, and roll it out as a premium feature to differentiate from competitors’ new advisor tools.</t>
+          <t>Launch a targeted outreach campaign to travel advisors, highlighting MONDEE’s API capabilities and integration benefits, and host a webinar series to demonstrate how our tools can streamline agency operations, directly countering Expedia TAAP’s new features. Track engagement metrics and adjust messaging based on advisor feedback.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a back‑office API for travel advisors that offers real‑time inventory, booking reference, and commission tracking, mirroring Expedia TAAP’s new tools but adding a mobile‑first UI and AI‑driven pricing suggestions to differentiate our offering.</t>
+          <t>Launch a back‑office API suite for travel advisors that includes real‑time inventory, booking reference tools, and AI‑driven pricing, directly addressing the feature set Expedia TAAP just released. Prioritize integration with major OTA partners to ensure seamless data flow and position MONDEE as the most efficient advisor tool in the market.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network’s platform, enabling boutique agencies to brand our inventory and booking tools while we capture a share of the growing white‑label market.</t>
+          <t>Create a dedicated travel‑advisor portal for Vancouver’s new car‑free Granville Street, offering exclusive event packages and real‑time pedestrian zone data, leveraging the increased foot traffic highlighted by Downtown Travel. Promote this portal through local tourism boards and social media to capture the growing demand for curated downtown experiences.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s city council to create a curated travel package highlighting the new car‑free Granville Street, positioning MONDEE as the go‑to platform for sustainable, city‑centric travel experiences.</t>
+          <t>Form a co‑branding partnership with Priceline Partner Network to embed MONDEE’s booking engine into their white‑label platform, expanding reach to agencies already using their system. Offer joint marketing and revenue‑sharing incentives to agencies to accelerate adoption and differentiate MONDEE from competitors.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite that lets travel advisors manage bookings, inventory, and reporting directly from MONDEE, mirroring Expedia TAAP’s new tools, and pilot it with our top 10 agency partners within 90 days. Include real‑time analytics dashboards and automated commission calculations to reduce manual effort.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with MONDEE’s existing platform to enable agencies to manage bookings, inventory, and reporting from a single dashboard. Prioritize API security and real‑time data sync to ensure agencies can operate efficiently and reduce manual errors.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for advisors that offers instant cashback, travel credits, and exclusive partner discounts, launching a beta with 50 advisors by Q3 to counter Expedia TAAP’s rewards push.</t>
+          <t>Introduce a tiered rewards program for travel advisors that rewards higher booking volumes with exclusive benefits, similar to Expedia TAAP Rewards, to incentivize partner loyalty and increase channel sales. Launch the program within 90 days and promote it through targeted webinars and partner newsletters.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Secure a white‑label travel engine partnership or build an in‑house engine to provide agencies with a seamless booking interface, positioning MONDEE as a one‑stop solution and leveraging the momentum behind Priceline Partner Network’s quiet rollout.</t>
+          <t>Partner with a leading white‑label travel engine, such as Priceline Partner Network, to embed MONDEE’s AI‑powered itinerary optimization into their platform, expanding reach to agencies that rely on white‑label solutions. Negotiate a revenue‑share agreement and co‑brand the feature to accelerate adoption among mid‑market agencies.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2765,17 +2765,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Conduct a rapid technical audit of Expedia TAAP’s new back‑office API to map its capabilities against MONDEE’s current API, then release a version‑2 API that adds missing features such as real‑time inventory sync and automated commission calculations, ensuring partners can migrate without service disruption.</t>
+          <t>Conduct a rapid feature gap analysis of Expedia's new back-office API and prioritize development of comparable or superior APIs within MONDEE's platform, targeting a 30‑day sprint to close the gap.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Develop a plug‑in that allows MONDEE partners to import data directly from Expedia TAAP’s new tools, positioning MONDEE as the seamless integration layer and encouraging partners to stay within the MONDEE ecosystem while leveraging Expedia’s expanded back‑office functionality.</t>
+          <t>Launch a targeted marketing campaign that showcases MONDEE's existing back-office tools and upcoming enhancements, positioning the brand as a more integrated solution for travel operators.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leverage the new Expedia TAAP API to launch a partner‑centric analytics dashboard that aggregates performance metrics across both platforms, offering insights that Expedia’s tools lack and creating a new subscription revenue stream for MONDEE.</t>
+          <t>Pursue a strategic partnership with a specialized back-office software provider to bundle complementary tools, enabling MONDEE to offer a comprehensive suite faster than competitors.</t>
         </is>
       </c>
     </row>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Develop a dedicated connector that maps MONDEE’s inventory and booking data to Expedia TAAP’s new back‑office API, enabling our merchants to sync rates and availability directly with Expedia’s platform.</t>
+          <t>Accelerate the development of a back‑office API that offers real‑time inventory and booking management, and release a beta version to our top 10 agency partners within 30 days to directly compete with Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Launch a comparative performance study and publish a whitepaper demonstrating that MONDEE’s back‑office automation delivers faster processing times and lower operational costs than Expedia TAAP’s new tools.</t>
+          <t>Initiate a joint integration pilot with Expedia TAAP to demonstrate seamless interoperability, positioning MONDEE as the preferred partner for agencies that use both platforms and highlighting our unique data‑driven insights.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Propose a joint beta integration program with Expedia, offering early adopters of TAAP’s API exclusive access to MONDEE’s analytics dashboard and priority support, positioning us as the preferred partner for back‑office solutions.</t>
+          <t>Launch a targeted marketing campaign that showcases MONDEE’s existing back‑office automation features—such as faster processing times and lower costs—positioning them as superior to Expedia’s newly released tools for travel agencies seeking efficiency.</t>
         </is>
       </c>
     </row>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Initiate a rapid development sprint to build a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and launch a beta with a select group of agencies within 90 days to secure early adopters.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and promote it through targeted webinars to capture agency demand.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Secure a partnership with Vancouver’s tourism board to embed MONDEE’s real‑time pedestrian‑zone navigation and AR tour features into the Granville Street expansion, positioning us as the preferred tech partner for city‑wide travel experiences.</t>
+          <t>Create a Vancouver‑centric travel bundle that highlights the new car‑free Granville Street, using MONDEE’s data to offer exclusive itineraries and partner with local businesses for cross‑promotions.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label integration with Priceline Partner Network to offer MONDEE’s booking engine to other agencies, expanding our inventory reach and countering their quiet market penetration.</t>
+          <t>Integrate MONDEE’s booking engine with Priceline Partner Network’s white‑label platform to provide agencies with a seamless, branded experience, and negotiate revenue‑share terms to expand market reach.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API that provides real‑time inventory, booking reference, and commission management for travel advisors, mirroring Expedia TAAP’s new tools, and release it within 90 days to capture the advisor market. Include a developer portal and sample integrations to accelerate adoption.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a sandbox for agencies to integrate and test, positioning MONDEE as the go‑to platform for agency automation. Prioritize API documentation and developer support to accelerate adoption among mid‑size agencies.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label partnership with a major travel agency platform, positioning MONDEE’s booking engine as a plug‑and‑play solution similar to Priceline Partner Network’s model, and roll it out in the next quarter. Offer joint marketing and revenue‑sharing terms to incentivize early adoption.</t>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, enabling partners to brand and customize the booking experience, and target niche verticals such as corporate travel or experiential tours. Leverage existing data feeds to provide real‑time inventory and pricing, ensuring partners can compete with larger platforms.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Launch a targeted outreach campaign to travel advisors, highlighting MONDEE’s API capabilities and integration benefits, and host a webinar series to demonstrate how our tools can streamline agency operations, directly countering Expedia TAAP’s new features. Track engagement metrics and adjust messaging based on advisor feedback.</t>
+          <t>Collaborate with key travel advisors to pilot a new advisor‑centric feature set, including real‑time booking reference tools and workflow automation, and use the pilot data to refine the product roadmap. Publish case studies from early adopters to demonstrate ROI and attract additional agency clients.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite for travel advisors that includes real‑time inventory, booking reference tools, and AI‑driven pricing, directly addressing the feature set Expedia TAAP just released. Prioritize integration with major OTA partners to ensure seamless data flow and position MONDEE as the most efficient advisor tool in the market.</t>
+          <t>Launch a back‑office API suite for travel advisors that integrates booking, inventory, and commission management, mirroring Expedia TAAP, to retain agency partners and differentiate MONDEE’s platform. Develop a modular, developer‑friendly SDK that allows agencies to embed MONDEE’s core booking engine into their own portals within 90 days.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Create a dedicated travel‑advisor portal for Vancouver’s new car‑free Granville Street, offering exclusive event packages and real‑time pedestrian zone data, leveraging the increased foot traffic highlighted by Downtown Travel. Promote this portal through local tourism boards and social media to capture the growing demand for curated downtown experiences.</t>
+          <t>Partner with Vancouver city authorities to create a digital concierge service for the new Granville Street pedestrian zone, offering real‑time navigation, local business promotions, and exclusive offers to capture the increased foot traffic. Deploy a mobile app that aggregates local events, dining, and transport options, positioning MONDEE as the go‑to platform for downtown travelers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Form a co‑branding partnership with Priceline Partner Network to embed MONDEE’s booking engine into their white‑label platform, expanding reach to agencies already using their system. Offer joint marketing and revenue‑sharing incentives to agencies to accelerate adoption and differentiate MONDEE from competitors.</t>
+          <t>Build a white‑label travel engine similar to Priceline Partner Network, enabling third‑party agencies to brand MONDEE’s booking infrastructure and expand revenue streams. Offer a revenue‑share model and dedicated support to attract agencies looking to launch their own branded travel portals within 6 months.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with MONDEE’s existing platform to enable agencies to manage bookings, inventory, and reporting from a single dashboard. Prioritize API security and real‑time data sync to ensure agencies can operate efficiently and reduce manual errors.</t>
+          <t>Launch a dedicated back‑office API and suite of tools for travel advisors, mirroring Expedia TAAP’s offerings, and open a beta program for agencies to test and provide feedback.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for travel advisors that rewards higher booking volumes with exclusive benefits, similar to Expedia TAAP Rewards, to incentivize partner loyalty and increase channel sales. Launch the program within 90 days and promote it through targeted webinars and partner newsletters.</t>
+          <t>Form a strategic partnership with a leading travel agency network to embed MONDEE’s white‑label engine, positioning it as a direct competitor to Priceline Partner Network’s platform.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Partner with a leading white‑label travel engine, such as Priceline Partner Network, to embed MONDEE’s AI‑powered itinerary optimization into their platform, expanding reach to agencies that rely on white‑label solutions. Negotiate a revenue‑share agreement and co‑brand the feature to accelerate adoption among mid‑market agencies.</t>
+          <t>Introduce a rewards program for advisors who book through MONDEE, offering tiered incentives and exclusive benefits to drive adoption and loyalty, similar to Expedia TAAP Rewards.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2765,17 +2765,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Partner with Vancouver tourism authorities to create a curated 'Granville Street Experience' package and launch a dedicated mobile feature that highlights the new pedestrian zone, positioning MONDEE as the go-to platform for this unique downtown travel experience.</t>
+          <t>Conduct a rapid feature gap analysis of Expedia's new back-office API and prioritize development of comparable or superior APIs within MONDEE's platform, targeting a 30‑day sprint to close the gap.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Develop and release a suite of back‑office API tools that provide real‑time inventory, pricing, and analytics, mirroring Expedia TAAP’s new capabilities, to attract travel agencies seeking integrated tech solutions.</t>
+          <t>Launch a targeted marketing campaign that showcases MONDEE's existing back-office tools and upcoming enhancements, positioning the brand as a more integrated solution for travel operators.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Initiate a white‑label partnership program targeting US travel brands, offering MONDEE’s booking engine and data services to replicate Priceline’s model and expand our presence in the U.S. market.</t>
+          <t>Pursue a strategic partnership with a specialized back-office software provider to bundle complementary tools, enabling MONDEE to offer a comprehensive suite faster than competitors.</t>
         </is>
       </c>
     </row>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite that mirrors Expedia TAAP’s new tools, enabling partners to automate inventory, pricing, and booking workflows directly from MONDEE’s platform.</t>
+          <t>Accelerate the development of a back‑office API that offers real‑time inventory and booking management, and release a beta version to our top 10 agency partners within 30 days to directly compete with Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Create a rapid integration module that plugs into Expedia TAAP’s API, allowing existing Expedia partners to migrate to MONDEE’s platform with minimal code changes and zero downtime.</t>
+          <t>Initiate a joint integration pilot with Expedia TAAP to demonstrate seamless interoperability, positioning MONDEE as the preferred partner for agencies that use both platforms and highlighting our unique data‑driven insights.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Run a targeted marketing campaign showcasing MONDEE’s advanced analytics and real‑time reporting for back‑office operations, positioning it as a more flexible and cost‑effective alternative to Expedia TAAP’s new offerings.</t>
+          <t>Launch a targeted marketing campaign that showcases MONDEE’s existing back‑office automation features—such as faster processing times and lower costs—positioning them as superior to Expedia’s newly released tools for travel agencies seeking efficiency.</t>
         </is>
       </c>
     </row>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API that offers real‑time inventory, dynamic pricing, and automated booking reference generation, directly addressing the feature set introduced by Expedia TAAP, and launch a targeted marketing campaign to travel advisors highlighting MONDEE’s superior integration capabilities.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and promote it through targeted webinars to capture agency demand.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism authority to create a mobile app that guides visitors through the new car‑free Granville Street zone, offering exclusive deals and real‑time navigation, thereby positioning MONDEE as the go‑to platform for the expanded downtown travel experience.</t>
+          <t>Create a Vancouver‑centric travel bundle that highlights the new car‑free Granville Street, using MONDEE’s data to offer exclusive itineraries and partner with local businesses for cross‑promotions.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine similar to Priceline Partner Network’s model, but with a focus on niche boutique agencies, and offer a revenue‑share partnership to quickly capture market share in the agency segment.</t>
+          <t>Integrate MONDEE’s booking engine with Priceline Partner Network’s white‑label platform to provide agencies with a seamless, branded experience, and negotiate revenue‑share terms to expand market reach.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Deploy a back‑office API that gives travel advisors programmatic access to inventory, booking, and reporting, mirroring Expedia TAAP’s new tools; launch a beta with key agency partners within 60 days. This will position MONDEE as the go‑to platform for agency automation.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a sandbox for agencies to integrate and test, positioning MONDEE as the go‑to platform for agency automation. Prioritize API documentation and developer support to accelerate adoption among mid‑size agencies.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine offering, allowing agencies to embed MONDEE’s booking capabilities under their own brand, similar to Priceline Partner Network; target 10 agencies in the next quarter.</t>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, enabling partners to brand and customize the booking experience, and target niche verticals such as corporate travel or experiential tours. Leverage existing data feeds to provide real‑time inventory and pricing, ensuring partners can compete with larger platforms.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Add advisor‑centric features such as automated booking reference generation, real‑time inventory sync, and a streamlined workflow dashboard, directly addressing the efficiency gains highlighted in Expedia TAAP’s launch; roll out the update in 45 days.</t>
+          <t>Collaborate with key travel advisors to pilot a new advisor‑centric feature set, including real‑time booking reference tools and workflow automation, and use the pilot data to refine the product roadmap. Publish case studies from early adopters to demonstrate ROI and attract additional agency clients.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite that mirrors Expedia TAAP’s new tools, adding real‑time inventory visibility and AI‑driven pricing recommendations, and pilot it with 3 high‑volume travel agencies to capture early adopters.</t>
+          <t>Launch a back‑office API suite for travel advisors that integrates booking, inventory, and commission management, mirroring Expedia TAAP, to retain agency partners and differentiate MONDEE’s platform. Develop a modular, developer‑friendly SDK that allows agencies to embed MONDEE’s core booking engine into their own portals within 90 days.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Create a dedicated Vancouver travel package that highlights the new car‑free Granville Street, integrating exclusive access passes and local experiences. Promote it through MONDEE’s platform to attract eco‑conscious travelers.</t>
+          <t>Partner with Vancouver city authorities to create a digital concierge service for the new Granville Street pedestrian zone, offering real‑time navigation, local business promotions, and exclusive offers to capture the increased foot traffic. Deploy a mobile app that aggregates local events, dining, and transport options, positioning MONDEE as the go‑to platform for downtown travelers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Offer a white‑label partnership with Priceline Partner Network’s engine, positioning MONDEE as a data‑rich alternative with lower commission rates. Target 5 mid‑market agencies to pilot the solution.</t>
+          <t>Build a white‑label travel engine similar to Priceline Partner Network, enabling third‑party agencies to brand MONDEE’s booking infrastructure and expand revenue streams. Offer a revenue‑share model and dedicated support to attract agencies looking to launch their own branded travel portals within 6 months.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel agencies, mirroring Expedia TAAP’s tools, to enable seamless booking and operational workflows within MONDEE’s platform.</t>
+          <t>Launch a dedicated back‑office API and suite of tools for travel advisors, mirroring Expedia TAAP’s offerings, and open a beta program for agencies to test and provide feedback.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for agencies that use MONDEE’s booking engine, similar to Expedia TAAP Rewards, to increase engagement and loyalty.</t>
+          <t>Form a strategic partnership with a leading travel agency network to embed MONDEE’s white‑label engine, positioning it as a direct competitor to Priceline Partner Network’s platform.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine offering for partner agencies, leveraging MONDEE’s technology to compete with Priceline Partner Network’s quiet engine.</t>
+          <t>Introduce a rewards program for advisors who book through MONDEE, offering tiered incentives and exclusive benefits to drive adoption and loyalty, similar to Expedia TAAP Rewards.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2765,17 +2765,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Conduct a rapid feature gap analysis of Expedia's new back-office API and prioritize development of comparable or superior APIs within MONDEE's platform, targeting a 30‑day sprint to close the gap.</t>
+          <t>Develop and launch a back‑office API that mirrors Expedia TAAP’s new tools, enabling our partners to integrate seamlessly with major OTA back‑end workflows. Prioritize real‑time inventory sync and automated commission calculations to match Expedia’s capabilities.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Launch a targeted marketing campaign that showcases MONDEE's existing back-office tools and upcoming enhancements, positioning the brand as a more integrated solution for travel operators.</t>
+          <t>Initiate a partnership pilot with Expedia to co‑integrate our API, offering joint customers a unified back‑office solution that leverages both platforms’ strengths. Use the pilot to gather data on usage patterns and refine our feature roadmap.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pursue a strategic partnership with a specialized back-office software provider to bundle complementary tools, enabling MONDEE to offer a comprehensive suite faster than competitors.</t>
+          <t>Conduct a rapid feature gap analysis of Expedia TAAP’s new tools, identify unmet needs in the market, and fast‑track development of complementary modules (e.g., dynamic pricing, reporting dashboards) to differentiate MONDEE.</t>
         </is>
       </c>
     </row>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Accelerate the development of a back‑office API that offers real‑time inventory and booking management, and release a beta version to our top 10 agency partners within 30 days to directly compete with Expedia TAAP’s new tools.</t>
+          <t>Launch a dedicated back‑office integration layer that mirrors Expedia TAAP’s new API, enabling our partners to sync reservations, inventory, and financials in real time, and promote it as a plug‑and‑play module in our marketplace.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Initiate a joint integration pilot with Expedia TAAP to demonstrate seamless interoperability, positioning MONDEE as the preferred partner for agencies that use both platforms and highlighting our unique data‑driven insights.</t>
+          <t>Initiate a joint beta program with Expedia to co‑develop a unified dashboard that aggregates data from both platforms, positioning MONDEE as the seamless bridge for agencies using multiple OTA APIs.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Launch a targeted marketing campaign that showcases MONDEE’s existing back‑office automation features—such as faster processing times and lower costs—positioning them as superior to Expedia’s newly released tools for travel agencies seeking efficiency.</t>
+          <t>Deploy a rapid‑response feature to auto‑generate back‑office reports for our clients, leveraging the new API endpoints, and launch a marketing campaign highlighting our enhanced reporting capabilities ahead of the next quarter.</t>
         </is>
       </c>
     </row>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and promote it through targeted webinars to capture agency demand.</t>
+          <t>Launch a back‑office API suite for travel advisors, offering a free pilot to the top 20 agencies in North America to secure early adoption.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Create a Vancouver‑centric travel bundle that highlights the new car‑free Granville Street, using MONDEE’s data to offer exclusive itineraries and partner with local businesses for cross‑promotions.</t>
+          <t>Develop a white‑label travel engine to compete with Priceline Partner Network, targeting mid‑size agencies that currently use third‑party platforms.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Integrate MONDEE’s booking engine with Priceline Partner Network’s white‑label platform to provide agencies with a seamless, branded experience, and negotiate revenue‑share terms to expand market reach.</t>
+          <t>Partner with Vancouver tourism authorities to create a mobile guide for the new car‑free Granville Street, integrating local events and real‑time navigation to showcase MONDEE’s urban travel expertise.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a sandbox for agencies to integrate and test, positioning MONDEE as the go‑to platform for agency automation. Prioritize API documentation and developer support to accelerate adoption among mid‑size agencies.</t>
+          <t>Launch a dedicated back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, and open a beta program for US advisors to integrate and provide feedback within 90 days.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, enabling partners to brand and customize the booking experience, and target niche verticals such as corporate travel or experiential tours. Leverage existing data feeds to provide real‑time inventory and pricing, ensuring partners can compete with larger platforms.</t>
+          <t>Secure a partnership with a white‑label travel engine provider (e.g., Priceline Partner Network) to bundle a customizable booking engine with MONDEE’s advisory platform, targeting agencies seeking a turnkey solution.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Collaborate with key travel advisors to pilot a new advisor‑centric feature set, including real‑time booking reference tools and workflow automation, and use the pilot data to refine the product roadmap. Publish case studies from early adopters to demonstrate ROI and attract additional agency clients.</t>
+          <t>Develop and roll out a real‑time booking reference and itinerary automation feature that reduces manual entry for advisors, and promote it through a targeted webinar series for travel agencies within the next 60 days.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite for travel advisors that integrates booking, inventory, and commission management, mirroring Expedia TAAP, to retain agency partners and differentiate MONDEE’s platform. Develop a modular, developer‑friendly SDK that allows agencies to embed MONDEE’s core booking engine into their own portals within 90 days.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel agencies that integrates real‑time inventory, booking reference, and commission management, positioning MONDEE as the most comprehensive agency platform in the market, and immediately begin beta testing with 3 key independent travel advisors.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Partner with Vancouver city authorities to create a digital concierge service for the new Granville Street pedestrian zone, offering real‑time navigation, local business promotions, and exclusive offers to capture the increased foot traffic. Deploy a mobile app that aggregates local events, dining, and transport options, positioning MONDEE as the go‑to platform for downtown travelers.</t>
+          <t>Secure a partnership with the City of Vancouver to provide a digital concierge service that promotes the new car‑free Granville Street, leveraging MONDEE’s existing travel recommendation engine to drive foot traffic and capture local commerce data for future monetization.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine similar to Priceline Partner Network, enabling third‑party agencies to brand MONDEE’s booking infrastructure and expand revenue streams. Offer a revenue‑share model and dedicated support to attract agencies looking to launch their own branded travel portals within 6 months.</t>
+          <t>Create a white‑label travel engine tailored for mid‑size OTA partners, mirroring Priceline Partner Network’s model, and launch a pilot with 2 emerging travel brands to capture market share in the white‑label segment.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API and suite of tools for travel advisors, mirroring Expedia TAAP’s offerings, and open a beta program for agencies to test and provide feedback.</t>
+          <t>Develop a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and launch a beta program with top independent agencies to gather feedback and secure early adopters. This will position MONDEE as the go‑to platform for agency efficiency and create a moat against Expedia’s TAAP.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Form a strategic partnership with a leading travel agency network to embed MONDEE’s white‑label engine, positioning it as a direct competitor to Priceline Partner Network’s platform.</t>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, enabling partners to brand MONDEE’s booking infrastructure, and target mid‑market agencies seeking cost‑effective solutions.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a rewards program for advisors who book through MONDEE, offering tiered incentives and exclusive benefits to drive adoption and loyalty, similar to Expedia TAAP Rewards.</t>
+          <t>Launch a tiered rewards program for advisors, akin to Expedia TAAP Rewards, offering commission boosts and exclusive training, to incentivize loyalty and differentiate MONDEE’s value proposition.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2765,17 +2765,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API that mirrors Expedia TAAP’s new tools, enabling our partners to integrate seamlessly with major OTA back‑end workflows. Prioritize real‑time inventory sync and automated commission calculations to match Expedia’s capabilities.</t>
+          <t>Market conditions are currently stable.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Initiate a partnership pilot with Expedia to co‑integrate our API, offering joint customers a unified back‑office solution that leverages both platforms’ strengths. Use the pilot to gather data on usage patterns and refine our feature roadmap.</t>
+          <t>No high-priority competitor moves detected in this timeframe.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Conduct a rapid feature gap analysis of Expedia TAAP’s new tools, identify unmet needs in the market, and fast‑track development of complementary modules (e.g., dynamic pricing, reporting dashboards) to differentiate MONDEE.</t>
+          <t>Continue tracking standard sector intelligence.</t>
         </is>
       </c>
     </row>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office integration layer that mirrors Expedia TAAP’s new API, enabling our partners to sync reservations, inventory, and financials in real time, and promote it as a plug‑and‑play module in our marketplace.</t>
+          <t>No competitor product launches or API releases cataloged.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Initiate a joint beta program with Expedia to co‑develop a unified dashboard that aggregates data from both platforms, positioning MONDEE as the seamless bridge for agencies using multiple OTA APIs.</t>
+          <t>Digital feature velocity remains normal.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deploy a rapid‑response feature to auto‑generate back‑office reports for our clients, leveraging the new API endpoints, and launch a marketing campaign highlighting our enhanced reporting capabilities ahead of the next quarter.</t>
+          <t>Continue monitoring competitor release notes.</t>
         </is>
       </c>
     </row>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite for travel advisors, offering a free pilot to the top 20 agencies in North America to secure early adoption.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s features, prioritizing real‑time inventory, booking reference tools, and workflow automation to attract agencies seeking a seamless tech stack.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine to compete with Priceline Partner Network, targeting mid‑size agencies that currently use third‑party platforms.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling partners to brand and sell curated itineraries while integrating with MONDEE’s core platform, thereby expanding our partner ecosystem.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver tourism authorities to create a mobile guide for the new car‑free Granville Street, integrating local events and real‑time navigation to showcase MONDEE’s urban travel expertise.</t>
+          <t>Create a Vancouver‑centric travel package API that highlights the new pedestrian zone, offering curated walking tours and local experiences, and promote it to travel agencies to capitalize on the city’s increased foot traffic.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, and open a beta program for US advisors to integrate and provide feedback within 90 days.</t>
+          <t>Develop a dedicated back-office API suite for travel advisors, mirroring Expedia TAAP's features, and partner with a major agency network to pilot it within 90 days.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Secure a partnership with a white‑label travel engine provider (e.g., Priceline Partner Network) to bundle a customizable booking engine with MONDEE’s advisory platform, targeting agencies seeking a turnkey solution.</t>
+          <t>Leverage our existing white-label engine to create a co-branded travel platform for a mid-sized agency, offering integrated booking and analytics, to compete with Priceline Partner Network's quiet engine.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Develop and roll out a real‑time booking reference and itinerary automation feature that reduces manual entry for advisors, and promote it through a targeted webinar series for travel agencies within the next 60 days.</t>
+          <t>Launch a targeted marketing campaign highlighting MONDEE's real-time data insights and AI-driven pricing tools, positioning us as the most efficient alternative to Expedia TAAP's new tools, and schedule a webinar for advisors within 30 days.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel agencies that integrates real‑time inventory, booking reference, and commission management, positioning MONDEE as the most comprehensive agency platform in the market, and immediately begin beta testing with 3 key independent travel advisors.</t>
+          <t>Develop a dedicated back‑office API for travel advisors that includes real‑time inventory, commission tracking, and automated booking reference generation, directly addressing Expedia TAAP’s new toolset and positioning MONDEE as the preferred tech partner for agencies.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Secure a partnership with the City of Vancouver to provide a digital concierge service that promotes the new car‑free Granville Street, leveraging MONDEE’s existing travel recommendation engine to drive foot traffic and capture local commerce data for future monetization.</t>
+          <t>Launch a city‑partner program that provides travel advisors with a specialized API for pedestrian‑zone itineraries, using Vancouver’s Granville Street expansion as a pilot to showcase sustainable travel solutions and differentiate MONDEE’s offerings.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine tailored for mid‑size OTA partners, mirroring Priceline Partner Network’s model, and launch a pilot with 2 emerging travel brands to capture market share in the white‑label segment.</t>
+          <t>Create a white‑label travel engine similar to Priceline Partner Network’s model, and secure exclusive distribution agreements with mid‑market agencies to capture the growing demand for customizable booking platforms.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and launch a beta program with top independent agencies to gather feedback and secure early adopters. This will position MONDEE as the go‑to platform for agency efficiency and create a moat against Expedia’s TAAP.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors that includes booking reference generation and real‑time inventory access, mirroring Expedia TAAP’s new tools, and offer it as a free pilot to top 50 agencies.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, enabling partners to brand MONDEE’s booking infrastructure, and target mid‑market agencies seeking cost‑effective solutions.</t>
+          <t>Introduce a rewards program for travel advisors that rewards higher booking volumes, directly competing with Expedia TAAP’s rewards, and integrate it into the API so advisors can track points in real time.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Launch a tiered rewards program for advisors, akin to Expedia TAAP Rewards, offering commission boosts and exclusive training, to incentivize loyalty and differentiate MONDEE’s value proposition.</t>
+          <t>Partner with a white‑label travel engine provider (e.g., Priceline Partner Network) to quickly roll out a customizable booking engine for agencies, positioning MONDEE as a one‑stop solution for agencies seeking both front‑end and back‑office capabilities.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s features, prioritizing real‑time inventory, booking reference tools, and workflow automation to attract agencies seeking a seamless tech stack.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a free pilot to the top 50 US agencies to secure early adoption.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling partners to brand and sell curated itineraries while integrating with MONDEE’s core platform, thereby expanding our partner ecosystem.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network, targeting mid‑market OTA partners in emerging markets to expand MONDEE’s distribution footprint.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a Vancouver‑centric travel package API that highlights the new pedestrian zone, offering curated walking tours and local experiences, and promote it to travel agencies to capitalize on the city’s increased foot traffic.</t>
+          <t>Create a localized travel package and marketing campaign for Vancouver’s new pedestrian zone, partnering with local tourism boards to position MONDEE as the go‑to platform for city‑centric experiences.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop a dedicated back-office API suite for travel advisors, mirroring Expedia TAAP's features, and partner with a major agency network to pilot it within 90 days.</t>
+          <t>Develop and release a back‑office API that allows travel agencies to pull booking references, manage inventory, and automate invoicing directly from MONDEE, mirroring Expedia TAAP’s new tools, and beta‑test it with 5 key agency partners within 30 days.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Leverage our existing white-label engine to create a co-branded travel platform for a mid-sized agency, offering integrated booking and analytics, to compete with Priceline Partner Network's quiet engine.</t>
+          <t>Secure a white‑label partnership with a travel engine like Priceline Partner Network to embed MONDEE’s itinerary‑management UI into their booking platform, creating a bundled solution that counters Expedia TAAP’s agency‑centric offerings.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Launch a targeted marketing campaign highlighting MONDEE's real-time data insights and AI-driven pricing tools, positioning us as the most efficient alternative to Expedia TAAP's new tools, and schedule a webinar for advisors within 30 days.</t>
+          <t>Launch a targeted outreach program to US travel advisors, offering a free pilot of MONDEE’s advisor‑toolset (real‑time pricing alerts, itinerary suggestions) and a dedicated API for agency workflow integration, to capture market share from agencies adopting Expedia TAAP.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop a dedicated back‑office API for travel advisors that includes real‑time inventory, commission tracking, and automated booking reference generation, directly addressing Expedia TAAP’s new toolset and positioning MONDEE as the preferred tech partner for agencies.</t>
+          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, focusing on real‑time booking reference management and workflow automation, and launch a pilot with 10 key agencies within 90 days.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Launch a city‑partner program that provides travel advisors with a specialized API for pedestrian‑zone itineraries, using Vancouver’s Granville Street expansion as a pilot to showcase sustainable travel solutions and differentiate MONDEE’s offerings.</t>
+          <t>Integrate MONDEE’s booking engine with Priceline Partner Network’s white‑label platform to offer a co‑branded solution, and negotiate a revenue‑share agreement with Priceline within 60 days to capture a share of their partner traffic.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine similar to Priceline Partner Network’s model, and secure exclusive distribution agreements with mid‑market agencies to capture the growing demand for customizable booking platforms.</t>
+          <t>Create a curated 'Granville Street Experience' travel package that highlights Vancouver’s car‑free zone, partner with local tourism boards and travel advisors, and promote it through targeted digital campaigns within 30 days.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors that includes booking reference generation and real‑time inventory access, mirroring Expedia TAAP’s new tools, and offer it as a free pilot to top 50 agencies.</t>
+          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s booking reference and workflow tools, integrating it with MONDEE’s existing advisor portal to enable real‑time inventory and commission management.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a rewards program for travel advisors that rewards higher booking volumes, directly competing with Expedia TAAP’s rewards, and integrate it into the API so advisors can track points in real time.</t>
+          <t>Launch a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand MONDEE’s booking platform and access our inventory, thereby positioning MONDEE as a direct competitor to the Booking Holdings engine.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Partner with a white‑label travel engine provider (e.g., Priceline Partner Network) to quickly roll out a customizable booking engine for agencies, positioning MONDEE as a one‑stop solution for agencies seeking both front‑end and back‑office capabilities.</t>
+          <t>Introduce a tiered rewards program for advisors, offering commission boosts and exclusive perks, directly countering Expedia TAAP’s rewards initiative and incentivizing partner loyalty.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a free pilot to the top 50 US agencies to secure early adoption.</t>
+          <t>Launch a dedicated back‑office API for travel advisors that includes real‑time inventory, automated booking reference generation, and AI‑driven pricing, mirroring Expedia TAAP’s new tools but with a focus on small‑to‑mid sized agencies. Prioritize integration with existing CRM platforms to reduce onboarding friction.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network, targeting mid‑market OTA partners in emerging markets to expand MONDEE’s distribution footprint.</t>
+          <t>Partner with a Vancouver travel agency to create a curated package that highlights the new car‑free Granville Street experience, positioning MONDEE as the go‑to platform for sustainable urban travel. Promote this package through targeted social media campaigns and local influencer collaborations.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a localized travel package and marketing campaign for Vancouver’s new pedestrian zone, partnering with local tourism boards to position MONDEE as the go‑to platform for city‑centric experiences.</t>
+          <t>Negotiate a white‑label partnership with Priceline Partner Network to embed MONDEE’s travel engine into their platform, offering a differentiated product that competes with Booking Holdings’ engine. Leverage this partnership to gain access to Priceline’s global distribution network and share revenue on each booking.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API that allows travel agencies to pull booking references, manage inventory, and automate invoicing directly from MONDEE, mirroring Expedia TAAP’s new tools, and beta‑test it with 5 key agency partners within 30 days.</t>
+          <t>Launch a back‑office API and toolset for travel advisors that mirrors Expedia TAAP’s offerings, enabling agencies to manage bookings, inventory, and reporting directly within MONDEE’s platform.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Secure a white‑label partnership with a travel engine like Priceline Partner Network to embed MONDEE’s itinerary‑management UI into their booking platform, creating a bundled solution that counters Expedia TAAP’s agency‑centric offerings.</t>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand and customize our booking engine while leveraging our inventory and pricing data.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Launch a targeted outreach program to US travel advisors, offering a free pilot of MONDEE’s advisor‑toolset (real‑time pricing alerts, itinerary suggestions) and a dedicated API for agency workflow integration, to capture market share from agencies adopting Expedia TAAP.</t>
+          <t>Deploy a suite of advisor‑centric features—such as automated booking reference generation, real‑time inventory alerts, and a unified dashboard—to improve operational efficiency and position MONDEE as the go‑to platform for travel agencies.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, focusing on real‑time booking reference management and workflow automation, and launch a pilot with 10 key agencies within 90 days.</t>
+          <t>Launch a back‑office API and tools suite for travel advisors, mirroring Expedia TAAP’s recent rollout, and partner with a select group of agencies to pilot the integration, gathering feedback for rapid iteration. This will position MONDEE as the go‑to platform for agency efficiency and counter Expedia’s market share gains.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Integrate MONDEE’s booking engine with Priceline Partner Network’s white‑label platform to offer a co‑branded solution, and negotiate a revenue‑share agreement with Priceline within 60 days to capture a share of their partner traffic.</t>
+          <t>Capitalize on Vancouver’s new pedestrian zone by creating a curated ‘Granville Street Experience’ package, bundling local attractions and transport, and promote it through our mobile app to attract travelers seeking unique urban experiences.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Create a curated 'Granville Street Experience' travel package that highlights Vancouver’s car‑free zone, partner with local tourism boards and travel advisors, and promote it through targeted digital campaigns within 30 days.</t>
+          <t>Develop a white‑label travel engine with AI‑driven personalization that can be resold to partners, differentiating from Priceline’s neutral offering, and launch a targeted outreach to boutique travel agencies looking for advanced tech solutions.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s booking reference and workflow tools, integrating it with MONDEE’s existing advisor portal to enable real‑time inventory and commission management.</t>
+          <t>Develop and release a back‑office API suite for travel agencies that mirrors Expedia TAAP’s new tools, including booking reference management and real‑time inventory. Launch a beta program with top independent agencies to gather feedback and iterate quickly.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand MONDEE’s booking platform and access our inventory, thereby positioning MONDEE as a direct competitor to the Booking Holdings engine.</t>
+          <t>Introduce a partner‑centric rewards program similar to Expedia TAAP Rewards, offering tiered incentives for agencies that book through MONDEE’s platform, and promote it via targeted email campaigns to existing agency clients.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for advisors, offering commission boosts and exclusive perks, directly countering Expedia TAAP’s rewards initiative and incentivizing partner loyalty.</t>
+          <t>Build a white‑label travel engine that can be embedded by partners, leveraging MONDEE’s existing booking infrastructure, and market it as a discreet, high‑performance alternative to Priceline Partner Network’s engine, with a dedicated partner portal for easy integration.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API for travel advisors that includes real‑time inventory, automated booking reference generation, and AI‑driven pricing, mirroring Expedia TAAP’s new tools but with a focus on small‑to‑mid sized agencies. Prioritize integration with existing CRM platforms to reduce onboarding friction.</t>
+          <t>Develop and release a back‑office API suite for travel agencies, enabling real‑time booking, reference, and reporting, directly addressing the gap left by Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with a Vancouver travel agency to create a curated package that highlights the new car‑free Granville Street experience, positioning MONDEE as the go‑to platform for sustainable urban travel. Promote this package through targeted social media campaigns and local influencer collaborations.</t>
+          <t>Partner with Booking Holdings to build a white‑label travel engine that can be embedded in third‑party platforms, leveraging the momentum of Priceline Partner Network’s quiet expansion.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label partnership with Priceline Partner Network to embed MONDEE’s travel engine into their platform, offering a differentiated product that competes with Booking Holdings’ engine. Leverage this partnership to gain access to Priceline’s global distribution network and share revenue on each booking.</t>
+          <t>Launch a mobile‑first, location‑based experience app for Vancouver’s Granville Street pedestrian zone, offering curated tours and real‑time event updates to capture the new downtown travel traffic.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a back‑office API and toolset for travel advisors that mirrors Expedia TAAP’s offerings, enabling agencies to manage bookings, inventory, and reporting directly within MONDEE’s platform.</t>
+          <t>Launch a back‑office API suite tailored for travel advisors, integrating real‑time booking reference tools and automated workflow features, and pilot it with a leading agency to showcase operational efficiency gains.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand and customize our booking engine while leveraging our inventory and pricing data.</t>
+          <t>Develop a white‑label travel engine that partners can embed into their own sites, offering a revenue‑sharing model to attract agencies and compete directly with Priceline’s quiet engine.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deploy a suite of advisor‑centric features—such as automated booking reference generation, real‑time inventory alerts, and a unified dashboard—to improve operational efficiency and position MONDEE as the go‑to platform for travel agencies.</t>
+          <t>Create a dedicated advisor portal with analytics dashboards and instant booking reference tools, and promote it through a targeted marketing campaign to position MONDEE as the most advisor‑friendly platform.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a back‑office API and tools suite for travel advisors, mirroring Expedia TAAP’s recent rollout, and partner with a select group of agencies to pilot the integration, gathering feedback for rapid iteration. This will position MONDEE as the go‑to platform for agency efficiency and counter Expedia’s market share gains.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, focusing on real‑time booking reference and commission management, and promote it through a targeted webinar series for agencies.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Capitalize on Vancouver’s new pedestrian zone by creating a curated ‘Granville Street Experience’ package, bundling local attractions and transport, and promote it through our mobile app to attract travelers seeking unique urban experiences.</t>
+          <t>Secure a partnership with Vancouver’s city council to integrate MONDEE’s booking platform into the newly pedestrianized Granville Street events, offering exclusive travel packages and real‑time crowd‑sourced itinerary suggestions.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine with AI‑driven personalization that can be resold to partners, differentiating from Priceline’s neutral offering, and launch a targeted outreach to boutique travel agencies looking for advanced tech solutions.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling boutique agencies to brand MONDEE’s core booking technology, and launch a pilot program with three mid‑size agencies to validate the model.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel agencies that mirrors Expedia TAAP’s new tools, including booking reference management and real‑time inventory. Launch a beta program with top independent agencies to gather feedback and iterate quickly.</t>
+          <t>Launch a back‑office API and suite of tools for travel advisors that mirrors Expedia TAAP’s functionality, enabling agencies to manage bookings, references, and reporting directly within the MONDEE platform.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a partner‑centric rewards program similar to Expedia TAAP Rewards, offering tiered incentives for agencies that book through MONDEE’s platform, and promote it via targeted email campaigns to existing agency clients.</t>
+          <t>Secure a white‑label partnership with a leading travel agency network, positioning MONDEE’s engine as a discreet, scalable solution similar to Priceline Partner Network, and offer it to agencies under their own branding.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine that can be embedded by partners, leveraging MONDEE’s existing booking infrastructure, and market it as a discreet, high‑performance alternative to Priceline Partner Network’s engine, with a dedicated partner portal for easy integration.</t>
+          <t>Introduce a tiered rewards program for advisors that rewards higher booking volumes and platform engagement, directly competing with Expedia TAAP’s rewards initiative.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel agencies, enabling real‑time booking, reference, and reporting, directly addressing the gap left by Expedia TAAP’s new tools.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a free pilot to the top 20 agencies to capture early adopters.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with Booking Holdings to build a white‑label travel engine that can be embedded in third‑party platforms, leveraging the momentum of Priceline Partner Network’s quiet expansion.</t>
+          <t>Partner with Vancouver’s city council to embed MONDEE’s booking platform into the new Granville Street pedestrian zone. Offer exclusive promotions and real‑time itinerary updates for visitors.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Launch a mobile‑first, location‑based experience app for Vancouver’s Granville Street pedestrian zone, offering curated tours and real‑time event updates to capture the new downtown travel traffic.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling third‑party brands to launch branded booking experiences. Target mid‑market travel agencies for rapid deployment.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite tailored for travel advisors, integrating real‑time booking reference tools and automated workflow features, and pilot it with a leading agency to showcase operational efficiency gains.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with MONDEE’s existing booking engine to streamline agency workflows. Prioritize API documentation and a sandbox environment to accelerate partner adoption within the next 90 days.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine that partners can embed into their own sites, offering a revenue‑sharing model to attract agencies and compete directly with Priceline’s quiet engine.</t>
+          <t>Introduce a white‑label travel engine partnership program similar to Priceline Partner Network, offering agencies a customizable booking platform that embeds MONDEE’s data and pricing, thereby expanding our reach into agency‑centric markets. Pilot the program with 3 key agency partners by Q3 to validate revenue potential.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Create a dedicated advisor portal with analytics dashboards and instant booking reference tools, and promote it through a targeted marketing campaign to position MONDEE as the most advisor‑friendly platform.</t>
+          <t>Leverage MONDEE’s AI‑driven recommendation engine to create a value‑added advisor tool that surfaces personalized travel options, positioning us as a tech‑forward alternative to Expedia TAAP’s advisor features. Deploy a beta feature for top 10 advisors by end of month to gather feedback and iterate.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, focusing on real‑time booking reference and commission management, and promote it through a targeted webinar series for agencies.</t>
+          <t>Launch a dedicated back‑office API that extends TAAP’s capabilities by adding real‑time dynamic pricing and sustainability scoring, and immediately pilot it with a select group of US travel advisors to demonstrate added value. Offer a free integration sandbox to encourage rapid adoption and gather feedback for iterative improvement.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Secure a partnership with Vancouver’s city council to integrate MONDEE’s booking platform into the newly pedestrianized Granville Street events, offering exclusive travel packages and real‑time crowd‑sourced itinerary suggestions.</t>
+          <t>Negotiate a white‑label partnership with Priceline Partner Network to embed MONDEE’s flexible booking engine, positioning it as a more customizable alternative to their current platform. Simultaneously launch a marketing campaign highlighting MONDEE’s open‑API architecture to attract agencies seeking greater control.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling boutique agencies to brand MONDEE’s core booking technology, and launch a pilot program with three mid‑size agencies to validate the model.</t>
+          <t>Develop a city‑centric mobile experience that partners with Vancouver’s Granville Street pedestrian zone, providing real‑time walking tour guides, local vendor promotions, and carbon‑offset incentives. Leverage this partnership to collect user data and refine our sustainability metrics, reinforcing MONDEE’s brand as an eco‑friendly travel tech leader.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch a back‑office API and suite of tools for travel advisors that mirrors Expedia TAAP’s functionality, enabling agencies to manage bookings, references, and reporting directly within the MONDEE platform.</t>
+          <t>Develop a back‑office API and agency tools mirroring Expedia TAAP’s new suite, prioritizing real‑time inventory and commission tracking, and launch a pilot with 10 key agencies within 6 months.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Secure a white‑label partnership with a leading travel agency network, positioning MONDEE’s engine as a discreet, scalable solution similar to Priceline Partner Network, and offer it to agencies under their own branding.</t>
+          <t>Create a white‑label travel engine to rival Priceline Partner Network, enabling agencies to brand the platform; secure a partnership with 3 agencies for beta deployment in 4 months.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for advisors that rewards higher booking volumes and platform engagement, directly competing with Expedia TAAP’s rewards initiative.</t>
+          <t>Introduce a tiered rewards program for travel advisors to counter Expedia TAAP Rewards, linking points to booking volume and offering exclusive benefits; roll out the program within 3 months.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a free pilot to the top 20 agencies to capture early adopters.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, offering real‑time booking reference and workflow integration to attract agency partners and compete directly for their business.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s city council to embed MONDEE’s booking platform into the new Granville Street pedestrian zone. Offer exclusive promotions and real‑time itinerary updates for visitors.</t>
+          <t>Secure a partnership with Vancouver’s city council to embed MONDEE’s booking engine into the new car‑free Granville Street pedestrian zone, providing exclusive promotions and real‑time availability for visitors and leveraging the increased foot traffic.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling third‑party brands to launch branded booking experiences. Target mid‑market travel agencies for rapid deployment.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network’s model, enabling other agencies to brand MONDEE’s platform and capture a share of the quiet market that Priceline is quietly expanding.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with MONDEE’s existing booking engine to streamline agency workflows. Prioritize API documentation and a sandbox environment to accelerate partner adoption within the next 90 days.</t>
+          <t>Initiate a rapid development of a back‑office API suite for travel advisors, including booking reference and workflow automation tools, to directly compete with Expedia TAAP's new offerings; target a beta launch with key agency partners within 90 days.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine partnership program similar to Priceline Partner Network, offering agencies a customizable booking platform that embeds MONDEE’s data and pricing, thereby expanding our reach into agency‑centric markets. Pilot the program with 3 key agency partners by Q3 to validate revenue potential.</t>
+          <t>Launch a white‑label travel engine that allows partners to brand and customize the booking experience, mirroring Priceline Partner Network's model; secure a pilot partnership with a mid‑size OTA within 60 days to validate the solution.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Leverage MONDEE’s AI‑driven recommendation engine to create a value‑added advisor tool that surfaces personalized travel options, positioning us as a tech‑forward alternative to Expedia TAAP’s advisor features. Deploy a beta feature for top 10 advisors by end of month to gather feedback and iterate.</t>
+          <t>Enhance MONDEE's advisor platform with AI‑driven dynamic pricing and inventory optimization tools, providing advisors with real‑time insights that Expedia's current tools lack; roll out the AI module to existing advisors in the next 120 days.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API that extends TAAP’s capabilities by adding real‑time dynamic pricing and sustainability scoring, and immediately pilot it with a select group of US travel advisors to demonstrate added value. Offer a free integration sandbox to encourage rapid adoption and gather feedback for iterative improvement.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP, to enable seamless booking, reference, and reporting; partner with a few key agencies for beta testing and gather feedback before full rollout.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label partnership with Priceline Partner Network to embed MONDEE’s flexible booking engine, positioning it as a more customizable alternative to their current platform. Simultaneously launch a marketing campaign highlighting MONDEE’s open‑API architecture to attract agencies seeking greater control.</t>
+          <t>Build a white‑label travel engine similar to Priceline Partner Network, positioning MONDEE as a flexible platform for other travel brands; initiate outreach to mid‑size travel agencies and boutique operators to pilot the engine and secure early contracts.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Develop a city‑centric mobile experience that partners with Vancouver’s Granville Street pedestrian zone, providing real‑time walking tour guides, local vendor promotions, and carbon‑offset incentives. Leverage this partnership to collect user data and refine our sustainability metrics, reinforcing MONDEE’s brand as an eco‑friendly travel tech leader.</t>
+          <t>Leverage the Vancouver car‑free Granville Street expansion by creating a curated “Granville Summer” travel package that includes accommodation, local experiences, and transport; promote it through social media and partner with local tourism boards to capture the growing pedestrian‑centric travel market.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop a back‑office API and agency tools mirroring Expedia TAAP’s new suite, prioritizing real‑time inventory and commission tracking, and launch a pilot with 10 key agencies within 6 months.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and pilot it with a select group of high‑volume agencies to validate integration ease and revenue potential. This will position MONDEE as the go‑to platform for agency automation and open a new revenue stream through API licensing.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine to rival Priceline Partner Network, enabling agencies to brand the platform; secure a partnership with 3 agencies for beta deployment in 4 months.</t>
+          <t>Introduce a white‑label travel engine partnership model similar to Priceline Partner Network, enabling agencies to brand MONDEE’s booking engine, and offer a revenue‑sharing agreement to accelerate adoption among mid‑market agencies.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for travel advisors to counter Expedia TAAP Rewards, linking points to booking volume and offering exclusive benefits; roll out the program within 3 months.</t>
+          <t>Launch a tiered rewards program for travel advisors, incentivizing higher booking volumes and platform engagement, and integrate it with the new API to provide real‑time commission tracking and redemption.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, offering real‑time booking reference and workflow integration to attract agency partners and compete directly for their business.</t>
+          <t>Launch a back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, enabling agencies to manage bookings, references, and reporting directly within MONDEE’s platform.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Secure a partnership with Vancouver’s city council to embed MONDEE’s booking engine into the new car‑free Granville Street pedestrian zone, providing exclusive promotions and real‑time availability for visitors and leveraging the increased foot traffic.</t>
+          <t>Introduce a white‑label travel engine for partners, inspired by Priceline Partner Network, allowing agencies to brand and sell our inventory while benefiting from our data and pricing engine.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network’s model, enabling other agencies to brand MONDEE’s platform and capture a share of the quiet market that Priceline is quietly expanding.</t>
+          <t>Partner with Vancouver tourism authorities to create a mobile guide and booking widget for the new car‑free Granville Street zone, positioning MONDEE as the go‑to platform for urban travel experiences.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Initiate a rapid development of a back‑office API suite for travel advisors, including booking reference and workflow automation tools, to directly compete with Expedia TAAP's new offerings; target a beta launch with key agency partners within 90 days.</t>
+          <t>Develop and release a back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, and integrate it with MONDEE’s existing booking engine to enable agencies to manage inventory, pricing, and bookings from a single dashboard. Prioritize API documentation and a sandbox environment to accelerate agency onboarding within the next 90 days.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine that allows partners to brand and customize the booking experience, mirroring Priceline Partner Network's model; secure a pilot partnership with a mid‑size OTA within 60 days to validate the solution.</t>
+          <t>Launch a white‑label travel engine similar to Priceline Partner Network, allowing partners to brand and sell travel products under their own name while leveraging MONDEE’s inventory and pricing engine. Partner with at least three mid‑size travel agencies in Q3 to pilot the engine and gather feedback for iterative improvement.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Enhance MONDEE's advisor platform with AI‑driven dynamic pricing and inventory optimization tools, providing advisors with real‑time insights that Expedia's current tools lack; roll out the AI module to existing advisors in the next 120 days.</t>
+          <t>Introduce an AI‑powered advisor assistant that provides real‑time pricing insights and itinerary suggestions, differentiating MONDEE from competitors that focus solely on back‑office tools. Deploy the assistant as a plug‑in for the new API suite, targeting agencies that require advanced analytics, and launch a marketing campaign highlighting the time‑saving benefits.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP, to enable seamless booking, reference, and reporting; partner with a few key agencies for beta testing and gather feedback before full rollout.</t>
+          <t>Develop and release a back‑office API that allows travel advisors to manage bookings, reference tools, and operational workflows directly within MONDEE, directly countering Expedia TAAP’s new API suite.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine similar to Priceline Partner Network, positioning MONDEE as a flexible platform for other travel brands; initiate outreach to mid‑size travel agencies and boutique operators to pilot the engine and secure early contracts.</t>
+          <t>Partner with Vancouver’s tourism authority to create a curated travel package for the new car‑free Granville Street zone, leveraging the expansion to drive bookings through MONDEE’s platform.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Leverage the Vancouver car‑free Granville Street expansion by creating a curated “Granville Summer” travel package that includes accommodation, local experiences, and transport; promote it through social media and partner with local tourism boards to capture the growing pedestrian‑centric travel market.</t>
+          <t>Negotiate a white‑label integration with Priceline Partner Network to embed MONDEE’s booking engine into their platform, expanding distribution while offering a differentiated product to agencies.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and pilot it with a select group of high‑volume agencies to validate integration ease and revenue potential. This will position MONDEE as the go‑to platform for agency automation and open a new revenue stream through API licensing.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and provide a dedicated developer portal with real‑time analytics to accelerate agency adoption.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine partnership model similar to Priceline Partner Network, enabling agencies to brand MONDEE’s booking engine, and offer a revenue‑sharing agreement to accelerate adoption among mid‑market agencies.</t>
+          <t>Introduce a tiered rewards program for advisors using MONDEE’s platform, similar to Expedia TAAP Rewards, to boost engagement and create a loyalty loop.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Launch a tiered rewards program for travel advisors, incentivizing higher booking volumes and platform engagement, and integrate it with the new API to provide real‑time commission tracking and redemption.</t>
+          <t>Build or acquire a white‑label travel engine to offer agencies a customizable booking solution, directly competing with Priceline Partner Network’s engine.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, enabling agencies to manage bookings, references, and reporting directly within MONDEE’s platform.</t>
+          <t>Launch a dedicated back‑office API suite for travel agencies that integrates with MONDEE’s existing booking engine, mirroring Expedia TAAP’s new tools, to capture the advisor market and differentiate with real‑time inventory and commission management.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine for partners, inspired by Priceline Partner Network, allowing agencies to brand and sell our inventory while benefiting from our data and pricing engine.</t>
+          <t>Secure a white‑label partnership with a major travel platform (e.g., Priceline Partner Network) to embed MONDEE’s dynamic pricing and itinerary optimization engine, positioning MONDEE as the underlying technology for high‑volume agencies and offsetting Expedia’s TAAP advantage.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver tourism authorities to create a mobile guide and booking widget for the new car‑free Granville Street zone, positioning MONDEE as the go‑to platform for urban travel experiences.</t>
+          <t>Develop a localized “Granville Street Experience” travel package and partner with Vancouver city tourism boards to offer exclusive itineraries, leveraging the new pedestrian zone to attract eco‑conscious travelers and create a unique selling point against generic travel tech offerings.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, and integrate it with MONDEE’s existing booking engine to enable agencies to manage inventory, pricing, and bookings from a single dashboard. Prioritize API documentation and a sandbox environment to accelerate agency onboarding within the next 90 days.</t>
+          <t>Launch a dedicated back‑office API for travel advisors, enabling seamless integration with agency booking systems and providing real‑time inventory and pricing data; pilot this with a select group of key partners to refine the offering before a full rollout.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine similar to Priceline Partner Network, allowing partners to brand and sell travel products under their own name while leveraging MONDEE’s inventory and pricing engine. Partner with at least three mid‑size travel agencies in Q3 to pilot the engine and gather feedback for iterative improvement.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand and customize the platform while leveraging MONDEE’s inventory; initiate a partnership program targeting mid‑market agencies to accelerate adoption.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Introduce an AI‑powered advisor assistant that provides real‑time pricing insights and itinerary suggestions, differentiating MONDEE from competitors that focus solely on back‑office tools. Deploy the assistant as a plug‑in for the new API suite, targeting agencies that require advanced analytics, and launch a marketing campaign highlighting the time‑saving benefits.</t>
+          <t>Introduce a dynamic pricing and commission optimization tool for advisors, offering predictive analytics and automated rate adjustments that outperform Expedia’s current features; integrate this into the API suite to provide a compelling value proposition for agency clients.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API that allows travel advisors to manage bookings, reference tools, and operational workflows directly within MONDEE, directly countering Expedia TAAP’s new API suite.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that integrates real‑time inventory, booking reference, and commission management, positioning MONDEE as the most comprehensive agency platform in the market. Prioritize a beta release with key agency partners within 90 days to capture early adopters before Expedia’s TAAP rollout.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism authority to create a curated travel package for the new car‑free Granville Street zone, leveraging the expansion to drive bookings through MONDEE’s platform.</t>
+          <t>Develop a white‑label travel engine similar to Priceline’s, enabling third‑party agencies to brand MONDEE’s platform, and negotiate a revenue‑share model with major OTA partners to expand reach.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label integration with Priceline Partner Network to embed MONDEE’s booking engine into their platform, expanding distribution while offering a differentiated product to agencies.</t>
+          <t>Partner with city tourism boards (e.g., Vancouver) to create a mobile app that promotes car‑free zones and offers real‑time navigation, positioning MONDEE as a local experience provider and differentiating from competitors focused solely on bookings.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and provide a dedicated developer portal with real‑time analytics to accelerate agency adoption.</t>
+          <t>Initiate a rapid development sprint to build a back‑office API and booking‑reference tools for travel advisors, mirroring Expedia TAAP’s recent launch, and target a beta release to 20 key agencies within 4 months.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for advisors using MONDEE’s platform, similar to Expedia TAAP Rewards, to boost engagement and create a loyalty loop.</t>
+          <t>Secure a partnership with a major travel agency to pilot a white‑label travel engine, leveraging Priceline Partner Network’s model, and use the pilot to gather data for a full‑scale launch within 6 months.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Build or acquire a white‑label travel engine to offer agencies a customizable booking solution, directly competing with Priceline Partner Network’s engine.</t>
+          <t>Design and launch a tiered rewards program for travel advisors, similar to Expedia TAAP Rewards, offering commission boosts and exclusive benefits, and roll it out to existing MONDEE partners within 3 months.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel agencies that integrates with MONDEE’s existing booking engine, mirroring Expedia TAAP’s new tools, to capture the advisor market and differentiate with real‑time inventory and commission management.</t>
+          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, allowing agencies to manage bookings, references, and operations directly within MONDEE’s platform. This will position MONDEE as a direct alternative to TAAP for agency clients.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Secure a white‑label partnership with a major travel platform (e.g., Priceline Partner Network) to embed MONDEE’s dynamic pricing and itinerary optimization engine, positioning MONDEE as the underlying technology for high‑volume agencies and offsetting Expedia’s TAAP advantage.</t>
+          <t>Partner with Vancouver’s tourism authority to promote the new car‑free Granville Street zone, offering exclusive travel packages and real‑time itinerary updates through MONDEE’s app. This leverages the positive buzz around the expansion and differentiates MONDEE’s advisory services.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Develop a localized “Granville Street Experience” travel package and partner with Vancouver city tourism boards to offer exclusive itineraries, leveraging the new pedestrian zone to attract eco‑conscious travelers and create a unique selling point against generic travel tech offerings.</t>
+          <t>Negotiate a white‑label integration with Priceline Partner Network to embed MONDEE’s travel engine into their platform, expanding reach while maintaining brand differentiation through unique advisory features. This counters Priceline’s quiet engine power and opens new revenue streams.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API for travel advisors, enabling seamless integration with agency booking systems and providing real‑time inventory and pricing data; pilot this with a select group of key partners to refine the offering before a full rollout.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s features, and offer a free pilot to the top 20 agencies to accelerate adoption.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand and customize the platform while leveraging MONDEE’s inventory; initiate a partnership program targeting mid‑market agencies to accelerate adoption.</t>
+          <t>Build a white‑label travel engine similar to Priceline Partner Network, enabling partners to embed MONDEE’s inventory and booking capabilities under their own brand, and target mid‑market agencies currently using Expedia TAAP.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Introduce a dynamic pricing and commission optimization tool for advisors, offering predictive analytics and automated rate adjustments that outperform Expedia’s current features; integrate this into the API suite to provide a compelling value proposition for agency clients.</t>
+          <t>Integrate AI‑driven workflow automation into MONDEE’s platform to help advisors manage bookings and references more efficiently, positioning it as a productivity enhancer beyond simple API access.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that integrates real‑time inventory, booking reference, and commission management, positioning MONDEE as the most comprehensive agency platform in the market. Prioritize a beta release with key agency partners within 90 days to capture early adopters before Expedia’s TAAP rollout.</t>
+          <t>Develop a back‑office API for travel advisors that offers real‑time inventory sync and AI pricing, directly addressing Expedia TAAP’s new tools and positioning MONDEE as the preferred platform for agencies.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline’s, enabling third‑party agencies to brand MONDEE’s platform, and negotiate a revenue‑share model with major OTA partners to expand reach.</t>
+          <t>Partner with Vancouver’s tourism board to launch a branded travel package centered on the new car‑free Granville Street zone, capitalizing on the positive momentum of Downtown Travel’s expansion.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Partner with city tourism boards (e.g., Vancouver) to create a mobile app that promotes car‑free zones and offers real‑time navigation, positioning MONDEE as a local experience provider and differentiating from competitors focused solely on bookings.</t>
+          <t>Introduce a white‑label travel engine for agencies, mirroring Priceline Partner Network’s model, to attract agencies seeking a branded solution and to compete for the same market segment.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Initiate a rapid development sprint to build a back‑office API and booking‑reference tools for travel advisors, mirroring Expedia TAAP’s recent launch, and target a beta release to 20 key agencies within 4 months.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with our existing booking engine to streamline agency operations.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Secure a partnership with a major travel agency to pilot a white‑label travel engine, leveraging Priceline Partner Network’s model, and use the pilot to gather data for a full‑scale launch within 6 months.</t>
+          <t>Build a white‑label travel engine similar to Priceline Partner Network, enabling agencies to brand our platform while accessing our inventory and pricing, thereby capturing the agency market.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Design and launch a tiered rewards program for travel advisors, similar to Expedia TAAP Rewards, offering commission boosts and exclusive benefits, and roll it out to existing MONDEE partners within 3 months.</t>
+          <t>Introduce a tiered rewards program for advisors, offering commission boosts and exclusive benefits, directly competing with Expedia TAAP’s rewards and incentivizing partner loyalty.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, offering real‑time booking reference and workflow integration to attract agency partners and compete directly for their business.</t>
+          <t>Develop a back‑office API suite for travel agencies, offering a free pilot to the top 20 US advisors to secure early adoption and compete with Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Secure a partnership with Vancouver’s city council to embed MONDEE’s booking engine into the new car‑free Granville Street pedestrian zone, providing exclusive promotions and real‑time availability for visitors and leveraging the increased foot traffic.</t>
+          <t>Launch a white‑label travel engine that partners can brand, targeting mid‑market agencies currently using Expedia TAAP for back‑office solutions.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network’s model, enabling other agencies to brand MONDEE’s platform and capture a share of the quiet market that Priceline is quietly expanding.</t>
+          <t>Create a Vancouver‑centric travel package that highlights the new pedestrian zone, partnering with local businesses and influencers to capture the growing demand for walkable city experiences.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Initiate a rapid development of a back‑office API suite for travel advisors, including booking reference and workflow automation tools, to directly compete with Expedia TAAP's new offerings; target a beta launch with key agency partners within 90 days.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that includes real‑time booking reference and inventory management, and promote it through a targeted outreach program to agencies using Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine that allows partners to brand and customize the booking experience, mirroring Priceline Partner Network's model; secure a pilot partnership with a mid‑size OTA within 60 days to validate the solution.</t>
+          <t>Build a white‑label travel engine on MONDEE’s platform and offer it as a plug‑in to mid‑market agencies, positioning it as a cost‑effective alternative to Priceline Partner Network’s engine.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Enhance MONDEE's advisor platform with AI‑driven dynamic pricing and inventory optimization tools, providing advisors with real‑time insights that Expedia's current tools lack; roll out the AI module to existing advisors in the next 120 days.</t>
+          <t>Develop an AI‑driven advisor assistant that automates itinerary creation and upsell suggestions, and integrate it into the new API to give agencies a competitive edge over Expedia’s standard offerings.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP, to enable seamless booking, reference, and reporting; partner with a few key agencies for beta testing and gather feedback before full rollout.</t>
+          <t>Develop and launch a back‑office API for travel advisors that offers real‑time inventory, booking reference tools, and automated commission calculations. Promote it via a webinar series targeting US travel agencies to counter Expedia TAAP’s new offerings.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine similar to Priceline Partner Network, positioning MONDEE as a flexible platform for other travel brands; initiate outreach to mid‑size travel agencies and boutique operators to pilot the engine and secure early contracts.</t>
+          <t>Create a 'Granville Street Experience' package that bundles local attractions, dining, and walking tours. Partner with Vancouver businesses to offer exclusive discounts, leveraging the new pedestrian zone to attract tourists.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Leverage the Vancouver car‑free Granville Street expansion by creating a curated “Granville Summer” travel package that includes accommodation, local experiences, and transport; promote it through social media and partner with local tourism boards to capture the growing pedestrian‑centric travel market.</t>
+          <t>Build a white‑label travel engine focused on sustainability and local experiences. Pitch it to boutique agencies that want to differentiate from Priceline Partner Network’s generic engine.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and pilot it with a select group of high‑volume agencies to validate integration ease and revenue potential. This will position MONDEE as the go‑to platform for agency automation and open a new revenue stream through API licensing.</t>
+          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s booking reference and workflow tools, integrating it into MONDEE’s existing advisor portal to streamline agency operations.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine partnership model similar to Priceline Partner Network, enabling agencies to brand MONDEE’s booking engine, and offer a revenue‑sharing agreement to accelerate adoption among mid‑market agencies.</t>
+          <t>Introduce a tiered rewards program for advisors that offers commission boosts and exclusive perks, directly addressing Expedia TAAP’s reward initiative and incentivizing partner loyalty.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Launch a tiered rewards program for travel advisors, incentivizing higher booking volumes and platform engagement, and integrate it with the new API to provide real‑time commission tracking and redemption.</t>
+          <t>Launch a white‑label travel engine similar to Priceline Partner Network, enabling agencies to brand and resell MONDEE’s inventory while maintaining control over the user experience.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, allowing agencies to manage bookings, references, and operations directly within MONDEE’s platform. This will position MONDEE as a direct alternative to TAAP for agency clients.</t>
+          <t>Develop a back‑office API for travel advisors that includes real‑time data on city‑wide pedestrian zones like Vancouver’s Granville Street, positioning MONDEE as the go‑to platform for agencies seeking localized event integration.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism authority to promote the new car‑free Granville Street zone, offering exclusive travel packages and real‑time itinerary updates through MONDEE’s app. This leverages the positive buzz around the expansion and differentiates MONDEE’s advisory services.</t>
+          <t>Launch a white‑label travel engine partnership program for agencies, mirroring Priceline Partner Network’s model, to capture market share from Expedia TAAP’s agency tools.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label integration with Priceline Partner Network to embed MONDEE’s travel engine into their platform, expanding reach while maintaining brand differentiation through unique advisory features. This counters Priceline’s quiet engine power and opens new revenue streams.</t>
+          <t>Create a joint marketing campaign with Vancouver tourism authorities to promote the car‑free Granville Street experience through MONDEE’s booking platform, leveraging the recent expansion to attract new users.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s features, and offer a free pilot to the top 20 agencies to accelerate adoption.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s features, and beta‑test it with a select group of top agencies to secure early adoption and gather feedback.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine similar to Priceline Partner Network, enabling partners to embed MONDEE’s inventory and booking capabilities under their own brand, and target mid‑market agencies currently using Expedia TAAP.</t>
+          <t>Build a white‑label travel engine platform similar to Priceline Partner Network, enabling partners to embed MONDEE’s inventory and booking capabilities under their own brand, and market it to mid‑market agencies seeking cost‑effective tech solutions.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Integrate AI‑driven workflow automation into MONDEE’s platform to help advisors manage bookings and references more efficiently, positioning it as a productivity enhancer beyond simple API access.</t>
+          <t>Integrate AI‑driven workflow automation into the new API, offering real‑time pricing optimization and inventory alerts, to position MONDEE as the most efficient advisor tool and differentiate from competitors’ standard APIs.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop a back‑office API for travel advisors that offers real‑time inventory sync and AI pricing, directly addressing Expedia TAAP’s new tools and positioning MONDEE as the preferred platform for agencies.</t>
+          <t>Develop and launch a back‑office API and suite of tools for travel advisors, mirroring Expedia TAAP’s recent rollout. Pilot it with 3 high‑volume agencies to secure early adoption.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism board to launch a branded travel package centered on the new car‑free Granville Street zone, capitalizing on the positive momentum of Downtown Travel’s expansion.</t>
+          <t>Create a mobile‑first, AR‑enhanced guide for Vancouver’s new pedestrian Granville Street zone, partnering with local businesses to offer exclusive promotions. Launch the guide in Q3 to capture early traffic and position MONDEE as the go‑to platform for urban travel experiences.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine for agencies, mirroring Priceline Partner Network’s model, to attract agencies seeking a branded solution and to compete for the same market segment.</t>
+          <t>Leverage Priceline Partner Network’s white‑label engine by integrating it into MONDEE’s platform, offering agencies a customizable, white‑label booking solution. Target 5 mid‑market agencies in Q4 to validate the model and generate incremental revenue.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with our existing booking engine to streamline agency operations.</t>
+          <t>Develop and release a back‑office API that provides real‑time booking reference tools and agency‑centric dashboards, mirroring Expedia TAAP’s new API suite, to enable travel advisors to manage bookings directly within MONDEE.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine similar to Priceline Partner Network, enabling agencies to brand our platform while accessing our inventory and pricing, thereby capturing the agency market.</t>
+          <t>Launch a travel‑advisor rewards program that offers tiered incentives for bookings and referrals, directly competing with Expedia TAAP’s rewards, to increase advisor loyalty and volume.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for advisors, offering commission boosts and exclusive benefits, directly competing with Expedia TAAP’s rewards and incentivizing partner loyalty.</t>
+          <t>Negotiate a white‑label partnership with Priceline Partner Network to embed its engine into MONDEE’s platform, giving agencies a seamless, branded booking experience while expanding our market reach.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a back‑office API for travel advisors that includes real‑time data on city‑wide pedestrian zones like Vancouver’s Granville Street, positioning MONDEE as the go‑to platform for agencies seeking localized event integration.</t>
+          <t>Develop a back‑office API suite for travel agencies, offering a free pilot to the top 20 US advisors to secure early adoption and compete with Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine partnership program for agencies, mirroring Priceline Partner Network’s model, to capture market share from Expedia TAAP’s agency tools.</t>
+          <t>Launch a white‑label travel engine that partners can brand, targeting mid‑market agencies currently using Expedia TAAP for back‑office solutions.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a joint marketing campaign with Vancouver tourism authorities to promote the car‑free Granville Street experience through MONDEE’s booking platform, leveraging the recent expansion to attract new users.</t>
+          <t>Create a Vancouver‑centric travel package that highlights the new pedestrian zone, partnering with local businesses and influencers to capture the growing demand for walkable city experiences.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s features, and beta‑test it with a select group of top agencies to secure early adoption and gather feedback.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that includes real‑time booking reference and inventory management, and promote it through a targeted outreach program to agencies using Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine platform similar to Priceline Partner Network, enabling partners to embed MONDEE’s inventory and booking capabilities under their own brand, and market it to mid‑market agencies seeking cost‑effective tech solutions.</t>
+          <t>Build a white‑label travel engine on MONDEE’s platform and offer it as a plug‑in to mid‑market agencies, positioning it as a cost‑effective alternative to Priceline Partner Network’s engine.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Integrate AI‑driven workflow automation into the new API, offering real‑time pricing optimization and inventory alerts, to position MONDEE as the most efficient advisor tool and differentiate from competitors’ standard APIs.</t>
+          <t>Develop an AI‑driven advisor assistant that automates itinerary creation and upsell suggestions, and integrate it into the new API to give agencies a competitive edge over Expedia’s standard offerings.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API and suite of tools for travel advisors, mirroring Expedia TAAP’s recent rollout. Pilot it with 3 high‑volume agencies to secure early adoption.</t>
+          <t>Develop and launch a back‑office API for travel advisors that offers real‑time inventory, booking reference tools, and automated commission calculations. Promote it via a webinar series targeting US travel agencies to counter Expedia TAAP’s new offerings.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Create a mobile‑first, AR‑enhanced guide for Vancouver’s new pedestrian Granville Street zone, partnering with local businesses to offer exclusive promotions. Launch the guide in Q3 to capture early traffic and position MONDEE as the go‑to platform for urban travel experiences.</t>
+          <t>Create a 'Granville Street Experience' package that bundles local attractions, dining, and walking tours. Partner with Vancouver businesses to offer exclusive discounts, leveraging the new pedestrian zone to attract tourists.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Leverage Priceline Partner Network’s white‑label engine by integrating it into MONDEE’s platform, offering agencies a customizable, white‑label booking solution. Target 5 mid‑market agencies in Q4 to validate the model and generate incremental revenue.</t>
+          <t>Build a white‑label travel engine focused on sustainability and local experiences. Pitch it to boutique agencies that want to differentiate from Priceline Partner Network’s generic engine.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API that provides real‑time booking reference tools and agency‑centric dashboards, mirroring Expedia TAAP’s new API suite, to enable travel advisors to manage bookings directly within MONDEE.</t>
+          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s booking reference and workflow tools, integrating it into MONDEE’s existing advisor portal to streamline agency operations.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Launch a travel‑advisor rewards program that offers tiered incentives for bookings and referrals, directly competing with Expedia TAAP’s rewards, to increase advisor loyalty and volume.</t>
+          <t>Introduce a tiered rewards program for advisors that offers commission boosts and exclusive perks, directly addressing Expedia TAAP’s reward initiative and incentivizing partner loyalty.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label partnership with Priceline Partner Network to embed its engine into MONDEE’s platform, giving agencies a seamless, branded booking experience while expanding our market reach.</t>
+          <t>Launch a white‑label travel engine similar to Priceline Partner Network, enabling agencies to brand and resell MONDEE’s inventory while maintaining control over the user experience.</t>
         </is>
       </c>
     </row>

--- a/News_Intelligence/output/raw_news_database_Mondee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Mondee.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -2629,6 +2629,92 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Downtown Travel News</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Downtown+Travel%22+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.mychesco.com/a/news/regional/doylestown-street-closures-could-disrupt-downtown-travel-for-months/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:20:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Downtown Travel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Downtown Travel (Brand)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Doylestown Street Closures Could Disrupt Downtown Travel for Months - MyChesCo</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Alec Robson</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DOYLESTOWN, PA — Drivers should prepare for months of daytime and overnight road closures in downtown Doylestown as PECO Energy begins utility construction affecting sections of State Street and Main Street.
+Crews will close and detour one section of roadway at a time to minimize disruptions.
+Closures on State Street will occur between:
+Closures on Main Street will occur between State Street and Court Street. Drivers will be directed to use State Street and Court Street.
+Local access will be maintained throughout construction. Drivers should plan extra time when traveling through downtown Doylestown because backups and delays are expected. Seek alternate routes whenever possible, especially during business hours.
+The construction schedule is weather dependent and may change if conditions are unfavorable.
+With work expected to continue through early December, motorists should anticipate changing traffic patterns as different sections of State Street and Main Street are closed throughout the project.
+Do not let downtown road closures catch you by surprise. Check the latest road restrictions, detours and traffic alerts at the MyChesCo Traffic Center before heading out: https://www.mychesco.com/traffic/
+Support the local news that supports Chester County. MyChesCo delivers reliable, fact-based reporting and essential community resources—free for everyone. If you value that, click here to become a patron today.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:11:14</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>DOYLESTOWN, PA — Drivers should prepare for months of daytime and overnight road closures in downtown Doylestown as PECO Energy begins utility construction affecting sections of State Street and Main Street. Crews will close and detour one section of roadway at a time to minimize disruptions.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
